--- a/farming_dashboard.xlsx
+++ b/farming_dashboard.xlsx
@@ -37,9 +37,11 @@
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Settings!$A$1:$E$56</definedName>
     <definedName function="false" hidden="false" localSheetId="9" name="_xlnm.Print_Area" vbProcedure="false">Simulator!$A$1:$O$91</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">Soils!$A$1:$F$38</definedName>
+    <definedName function="false" hidden="false" name="ClimateRows" vbProcedure="false">Settings!$C$57</definedName>
     <definedName function="false" hidden="false" name="CropNames" vbProcedure="false">Crops!$B$5:$B$22</definedName>
     <definedName function="false" hidden="false" name="CurrentDay" vbProcedure="false">Settings!$C$55</definedName>
     <definedName function="false" hidden="false" name="DaysPerMonth" vbProcedure="false">Settings!$C$6</definedName>
+    <definedName function="false" hidden="false" name="DaysPerYear" vbProcedure="false">Settings!$C$9</definedName>
     <definedName function="false" hidden="false" name="DefaultCold" vbProcedure="false">Settings!$C$29</definedName>
     <definedName function="false" hidden="false" name="DefaultHeat" vbProcedure="false">Settings!$C$30</definedName>
     <definedName function="false" hidden="false" name="DefaultRipeMul" vbProcedure="false">Settings!$C$31</definedName>
@@ -71,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="919" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="925" uniqueCount="752">
   <si>
     <t xml:space="preserve">Vintage Story Farming Dashboard</t>
   </si>
@@ -82,7 +84,7 @@
     <t xml:space="preserve">What this is</t>
   </si>
   <si>
-    <t xml:space="preserve">A planning workbook for Vintage Story farming. The numbers come from the actual game files (vssurvivalmod source, crop JSONs, Specialized Classes mod IL), not from wiki guesses. Every formula traces back to specific code in SPEC.md.</t>
+    <t xml:space="preserve">A planning workbook for Vintage Story farming. The web app at https://garrethcline.github.io/vs-farming/ is the primary tool. This workbook is the math primer where the formulas were worked out before they got pushed into the React code. If you just want to plan a season, use the web app. If you want to read or audit the math cell-by-cell, this is where to look.</t>
   </si>
   <si>
     <t xml:space="preserve">Color legend (cell text colors)</t>
@@ -130,7 +132,7 @@
     <t xml:space="preserve">Settings</t>
   </si>
   <si>
-    <t xml:space="preserve">Global config: server constants, climate, growth/damage rules. Edit inputs here.</t>
+    <t xml:space="preserve">Global config: server constants, climate, growth/damage rules. DaysPerMonth, DaysPerYear, and ClimateRows are named ranges. Most date arithmetic on other sheets pulls from them, so changing DaysPerMonth scales the year wraps. The Climate sheet itself stays at 108 rows; for a different DaysPerMonth, regenerate climate.csv.</t>
   </si>
   <si>
     <t xml:space="preserve">Climate</t>
@@ -148,7 +150,7 @@
     <t xml:space="preserve">Soils</t>
   </si>
   <si>
-    <t xml:space="preserve">5 soil tiers + bony soil callout (NOT tillable!). Fertility values.</t>
+    <t xml:space="preserve">5 soil tiers (poor / medium / compost / dirt / terra preta). Fertility values per tier.</t>
   </si>
   <si>
     <t xml:space="preserve">Fertilizers</t>
@@ -160,7 +162,7 @@
     <t xml:space="preserve">Calendar</t>
   </si>
   <si>
-    <t xml:space="preserve">Plantability heatmap: 18 crops × 108 days, color-coded. Toggle greenhouse on/off.</t>
+    <t xml:space="preserve">Plantability heatmap across the full year. Toggle greenhouse on/off to compare.</t>
   </si>
   <si>
     <t xml:space="preserve">Simulator</t>
@@ -193,6 +195,15 @@
     <t xml:space="preserve">Glossary, key formulas explained, source citations.</t>
   </si>
   <si>
+    <t xml:space="preserve">What lives in the app but not here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rainfall + light/depth multipliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The web app Decision Helper multiplies a moisture factor (from biome rainfall) and a light/depth factor into grow speed. Those use Monte Carlo of the noise pipeline plus the formulas from BESoilNutrition.cs and BlockEntityFastForwardGrowth.cs. They are not in this spreadsheet yet; the app is the reference implementation.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quick start</t>
   </si>
   <si>
@@ -941,6 +952,15 @@
   </si>
   <si>
     <t xml:space="preserve">For Activity Log timestamps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClimateRows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rows</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How many rows of climate data exist on the Climate sheet. Tied to the climate.csv data, not the year. If you change DaysPerMonth, regenerate climate data to match.</t>
   </si>
   <si>
     <t xml:space="preserve">Climate  ·  daily temperatures at your settled location</t>
@@ -4062,9 +4082,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>147960</xdr:colOff>
+      <xdr:colOff>146880</xdr:colOff>
       <xdr:row>102</xdr:row>
-      <xdr:rowOff>75600</xdr:rowOff>
+      <xdr:rowOff>74520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4078,7 +4098,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="211320" y="20202480"/>
-          <a:ext cx="7619400" cy="2552040"/>
+          <a:ext cx="7618320" cy="2550960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4099,9 +4119,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>147960</xdr:colOff>
+      <xdr:colOff>146880</xdr:colOff>
       <xdr:row>127</xdr:row>
-      <xdr:rowOff>37440</xdr:rowOff>
+      <xdr:rowOff>36360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4115,7 +4135,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="211320" y="24012360"/>
-          <a:ext cx="7619400" cy="3466440"/>
+          <a:ext cx="7618320" cy="3465360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4136,9 +4156,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>147960</xdr:colOff>
+      <xdr:colOff>146880</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>142200</xdr:rowOff>
+      <xdr:rowOff>141120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4152,7 +4172,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="211320" y="28203480"/>
-          <a:ext cx="7619400" cy="3190320"/>
+          <a:ext cx="7618320" cy="3189240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4178,9 +4198,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>342360</xdr:colOff>
+      <xdr:colOff>341280</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>209160</xdr:rowOff>
+      <xdr:rowOff>208080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4194,7 +4214,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="141120" y="3657600"/>
-          <a:ext cx="8095680" cy="6285960"/>
+          <a:ext cx="8094600" cy="6284880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4220,9 +4240,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>329040</xdr:colOff>
+      <xdr:colOff>327960</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>151920</xdr:rowOff>
+      <xdr:rowOff>150840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4236,7 +4256,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8740080" y="685800"/>
-          <a:ext cx="7619400" cy="2571120"/>
+          <a:ext cx="7618320" cy="2570040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4257,9 +4277,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>329040</xdr:colOff>
+      <xdr:colOff>327960</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>189720</xdr:rowOff>
+      <xdr:rowOff>188640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4273,7 +4293,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8740080" y="5200560"/>
-          <a:ext cx="7619400" cy="2475720"/>
+          <a:ext cx="7618320" cy="2474640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4299,9 +4319,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>570960</xdr:colOff>
+      <xdr:colOff>569880</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>104040</xdr:rowOff>
+      <xdr:rowOff>102960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4315,7 +4335,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="846000" y="6858000"/>
-          <a:ext cx="7619400" cy="4104720"/>
+          <a:ext cx="7618320" cy="4103640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4336,9 +4356,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>570960</xdr:colOff>
+      <xdr:colOff>569880</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>123120</xdr:rowOff>
+      <xdr:rowOff>122040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4352,7 +4372,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="846000" y="12763440"/>
-          <a:ext cx="7619400" cy="3361680"/>
+          <a:ext cx="7618320" cy="3360600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4373,9 +4393,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>570960</xdr:colOff>
+      <xdr:colOff>569880</xdr:colOff>
       <xdr:row>106</xdr:row>
-      <xdr:rowOff>142200</xdr:rowOff>
+      <xdr:rowOff>141120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4389,7 +4409,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="846000" y="18478440"/>
-          <a:ext cx="7619400" cy="3761640"/>
+          <a:ext cx="7618320" cy="3760560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4415,9 +4435,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>2262600</xdr:colOff>
+      <xdr:colOff>2261520</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>122760</xdr:rowOff>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4431,7 +4451,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="281880" y="4800600"/>
-          <a:ext cx="7619400" cy="2980440"/>
+          <a:ext cx="7618320" cy="2979360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4457,9 +4477,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2719440</xdr:colOff>
+      <xdr:colOff>2718360</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>8640</xdr:rowOff>
+      <xdr:rowOff>7560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4473,7 +4493,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="281880" y="8238960"/>
-          <a:ext cx="6666840" cy="3247200"/>
+          <a:ext cx="6665760" cy="3246120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4494,9 +4514,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>2719440</xdr:colOff>
+      <xdr:colOff>2718360</xdr:colOff>
       <xdr:row>74</xdr:row>
-      <xdr:rowOff>46800</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4510,7 +4530,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="281880" y="13192200"/>
-          <a:ext cx="6666840" cy="3285360"/>
+          <a:ext cx="6665760" cy="3284280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4531,9 +4551,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>551520</xdr:colOff>
+      <xdr:colOff>550440</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>161280</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4547,7 +4567,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="10667880" y="4514760"/>
-          <a:ext cx="6666840" cy="3695040"/>
+          <a:ext cx="6665760" cy="3693960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4573,9 +4593,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
-      <xdr:colOff>45000</xdr:colOff>
+      <xdr:colOff>43920</xdr:colOff>
       <xdr:row>51</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:rowOff>55800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4589,7 +4609,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="5915160"/>
-          <a:ext cx="10476720" cy="4438080"/>
+          <a:ext cx="10475640" cy="4437000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4610,9 +4630,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>45</xdr:col>
-      <xdr:colOff>45000</xdr:colOff>
+      <xdr:colOff>43920</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>56880</xdr:rowOff>
+      <xdr:rowOff>55800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4626,7 +4646,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="11630160"/>
-          <a:ext cx="10476720" cy="4438080"/>
+          <a:ext cx="10475640" cy="4437000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4652,9 +4672,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>1557720</xdr:colOff>
+      <xdr:colOff>1556640</xdr:colOff>
       <xdr:row>75</xdr:row>
-      <xdr:rowOff>132840</xdr:rowOff>
+      <xdr:rowOff>131760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4668,7 +4688,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="281880" y="13782600"/>
-          <a:ext cx="7619400" cy="3752280"/>
+          <a:ext cx="7618320" cy="3751200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4694,9 +4714,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>27</xdr:col>
-      <xdr:colOff>353520</xdr:colOff>
+      <xdr:colOff>352440</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>66240</xdr:rowOff>
+      <xdr:rowOff>65160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4710,7 +4730,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17457480" y="1362240"/>
-          <a:ext cx="5714280" cy="4676040"/>
+          <a:ext cx="5713200" cy="4674960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5110,66 +5130,77 @@
         <v>39</v>
       </c>
     </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C31" s="6"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C32" s="6"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C33" s="6"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C34" s="6"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C35" s="6"/>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B39" s="18" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C39" s="18"/>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -5223,7 +5254,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -5234,7 +5265,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -5254,7 +5285,7 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -5266,40 +5297,40 @@
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38"/>
       <c r="B5" s="150" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C5" s="151" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D5" s="152" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="E5" s="38"/>
       <c r="F5" s="38"/>
       <c r="G5" s="38"/>
       <c r="J5" s="153" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="K5" s="154" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="L5" s="154" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="M5" s="154" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="N5" s="154" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="O5" s="154" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="45"/>
       <c r="B6" s="155" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C6" s="151" t="n">
         <v>50</v>
@@ -5312,7 +5343,7 @@
       <c r="F6" s="45"/>
       <c r="G6" s="45"/>
       <c r="J6" s="153" t="n">
-        <f aca="false">IF($C$6+0&gt;108,$C$6+0-108,$C$6+0)</f>
+        <f aca="false">IF($C$6+0&gt;DaysPerYear,$C$6+0-DaysPerYear,$C$6+0)</f>
         <v>50</v>
       </c>
       <c r="K6" s="154" t="n">
@@ -5339,19 +5370,19 @@
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="38"/>
       <c r="B7" s="150" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C7" s="151" t="n">
         <v>65</v>
       </c>
       <c r="D7" s="152" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="38"/>
       <c r="G7" s="38"/>
       <c r="J7" s="153" t="n">
-        <f aca="false">IF($C$6+1&gt;108,$C$6+1-108,$C$6+1)</f>
+        <f aca="false">IF($C$6+1&gt;DaysPerYear,$C$6+1-DaysPerYear,$C$6+1)</f>
         <v>51</v>
       </c>
       <c r="K7" s="154" t="n">
@@ -5378,20 +5409,20 @@
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="45"/>
       <c r="B8" s="155" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C8" s="157" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="D8" s="158" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="E8" s="45"/>
       <c r="F8" s="45"/>
       <c r="G8" s="45"/>
       <c r="J8" s="153" t="n">
-        <f aca="false">IF($C$6+2&gt;108,$C$6+2-108,$C$6+2)</f>
+        <f aca="false">IF($C$6+2&gt;DaysPerYear,$C$6+2-DaysPerYear,$C$6+2)</f>
         <v>52</v>
       </c>
       <c r="K8" s="154" t="n">
@@ -5418,20 +5449,20 @@
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="38"/>
       <c r="B9" s="150" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C9" s="159" t="n">
         <f aca="false">Moisture</f>
         <v>0.75</v>
       </c>
       <c r="D9" s="152" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="E9" s="38"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
       <c r="J9" s="153" t="n">
-        <f aca="false">IF($C$6+3&gt;108,$C$6+3-108,$C$6+3)</f>
+        <f aca="false">IF($C$6+3&gt;DaysPerYear,$C$6+3-DaysPerYear,$C$6+3)</f>
         <v>53</v>
       </c>
       <c r="K9" s="154" t="n">
@@ -5457,7 +5488,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J10" s="153" t="n">
-        <f aca="false">IF($C$6+4&gt;108,$C$6+4-108,$C$6+4)</f>
+        <f aca="false">IF($C$6+4&gt;DaysPerYear,$C$6+4-DaysPerYear,$C$6+4)</f>
         <v>54</v>
       </c>
       <c r="K10" s="154" t="n">
@@ -5483,7 +5514,7 @@
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -5492,7 +5523,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="J11" s="153" t="n">
-        <f aca="false">IF($C$6+5&gt;108,$C$6+5-108,$C$6+5)</f>
+        <f aca="false">IF($C$6+5&gt;DaysPerYear,$C$6+5-DaysPerYear,$C$6+5)</f>
         <v>55</v>
       </c>
       <c r="K11" s="154" t="n">
@@ -5519,20 +5550,20 @@
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="38"/>
       <c r="B12" s="152" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C12" s="94" t="n">
         <f aca="false">MATCH($C$5,CropNames,0)+4</f>
         <v>5</v>
       </c>
       <c r="D12" s="152" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="E12" s="38"/>
       <c r="F12" s="38"/>
       <c r="G12" s="38"/>
       <c r="J12" s="153" t="n">
-        <f aca="false">IF($C$6+6&gt;108,$C$6+6-108,$C$6+6)</f>
+        <f aca="false">IF($C$6+6&gt;DaysPerYear,$C$6+6-DaysPerYear,$C$6+6)</f>
         <v>56</v>
       </c>
       <c r="K12" s="154" t="n">
@@ -5559,7 +5590,7 @@
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="45"/>
       <c r="B13" s="160" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="C13" s="110" t="n">
         <f aca="false">INDEX(Crops!$D$5:$D$22,MATCH($C$5,CropNames,0))</f>
@@ -5569,10 +5600,10 @@
       <c r="E13" s="45"/>
       <c r="F13" s="45"/>
       <c r="G13" s="79" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="J13" s="153" t="n">
-        <f aca="false">IF($C$6+7&gt;108,$C$6+7-108,$C$6+7)</f>
+        <f aca="false">IF($C$6+7&gt;DaysPerYear,$C$6+7-DaysPerYear,$C$6+7)</f>
         <v>57</v>
       </c>
       <c r="K13" s="154" t="n">
@@ -5599,7 +5630,7 @@
     <row r="14" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="38"/>
       <c r="B14" s="161" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C14" s="159" t="n">
         <f aca="false">INDEX(Crops!$E$5:$E$22,MATCH($C$5,CropNames,0))</f>
@@ -5609,10 +5640,10 @@
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
       <c r="G14" s="76" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="J14" s="153" t="n">
-        <f aca="false">IF($C$6+8&gt;108,$C$6+8-108,$C$6+8)</f>
+        <f aca="false">IF($C$6+8&gt;DaysPerYear,$C$6+8-DaysPerYear,$C$6+8)</f>
         <v>58</v>
       </c>
       <c r="K14" s="154" t="n">
@@ -5639,7 +5670,7 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="45"/>
       <c r="B15" s="160" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="C15" s="106" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH($C$5,CropNames,0))</f>
@@ -5649,10 +5680,10 @@
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
       <c r="G15" s="79" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="J15" s="153" t="n">
-        <f aca="false">IF($C$6+9&gt;108,$C$6+9-108,$C$6+9)</f>
+        <f aca="false">IF($C$6+9&gt;DaysPerYear,$C$6+9-DaysPerYear,$C$6+9)</f>
         <v>59</v>
       </c>
       <c r="K15" s="154" t="n">
@@ -5679,7 +5710,7 @@
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38"/>
       <c r="B16" s="161" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C16" s="162" t="str">
         <f aca="false">INDEX(Crops!$G$5:$G$22,MATCH($C$5,CropNames,0))</f>
@@ -5689,10 +5720,10 @@
       <c r="E16" s="38"/>
       <c r="F16" s="38"/>
       <c r="G16" s="76" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="J16" s="153" t="n">
-        <f aca="false">IF($C$6+10&gt;108,$C$6+10-108,$C$6+10)</f>
+        <f aca="false">IF($C$6+10&gt;DaysPerYear,$C$6+10-DaysPerYear,$C$6+10)</f>
         <v>60</v>
       </c>
       <c r="K16" s="154" t="n">
@@ -5719,7 +5750,7 @@
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="45"/>
       <c r="B17" s="160" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C17" s="106" t="n">
         <f aca="false">INDEX(Crops!$H$5:$H$22,MATCH($C$5,CropNames,0))</f>
@@ -5729,10 +5760,10 @@
       <c r="E17" s="45"/>
       <c r="F17" s="45"/>
       <c r="G17" s="79" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="J17" s="153" t="n">
-        <f aca="false">IF($C$6+11&gt;108,$C$6+11-108,$C$6+11)</f>
+        <f aca="false">IF($C$6+11&gt;DaysPerYear,$C$6+11-DaysPerYear,$C$6+11)</f>
         <v>61</v>
       </c>
       <c r="K17" s="154" t="n">
@@ -5759,7 +5790,7 @@
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38"/>
       <c r="B18" s="161" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C18" s="159" t="n">
         <f aca="false">INDEX(Crops!$I$5:$I$22,MATCH($C$5,CropNames,0))</f>
@@ -5769,10 +5800,10 @@
       <c r="E18" s="38"/>
       <c r="F18" s="38"/>
       <c r="G18" s="76" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="J18" s="153" t="n">
-        <f aca="false">IF($C$6+12&gt;108,$C$6+12-108,$C$6+12)</f>
+        <f aca="false">IF($C$6+12&gt;DaysPerYear,$C$6+12-DaysPerYear,$C$6+12)</f>
         <v>62</v>
       </c>
       <c r="K18" s="154" t="n">
@@ -5799,7 +5830,7 @@
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="45"/>
       <c r="B19" s="160" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C19" s="110" t="n">
         <f aca="false">INDEX(Crops!$K$5:$K$22,MATCH($C$5,CropNames,0))</f>
@@ -5809,10 +5840,10 @@
       <c r="E19" s="45"/>
       <c r="F19" s="45"/>
       <c r="G19" s="79" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="J19" s="153" t="n">
-        <f aca="false">IF($C$6+13&gt;108,$C$6+13-108,$C$6+13)</f>
+        <f aca="false">IF($C$6+13&gt;DaysPerYear,$C$6+13-DaysPerYear,$C$6+13)</f>
         <v>63</v>
       </c>
       <c r="K19" s="154" t="n">
@@ -5839,7 +5870,7 @@
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38"/>
       <c r="B20" s="161" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="C20" s="101" t="n">
         <f aca="false">INDEX(Crops!$M$5:$M$22,MATCH($C$5,CropNames,0))</f>
@@ -5849,10 +5880,10 @@
       <c r="E20" s="38"/>
       <c r="F20" s="38"/>
       <c r="G20" s="76" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="J20" s="153" t="n">
-        <f aca="false">IF($C$6+14&gt;108,$C$6+14-108,$C$6+14)</f>
+        <f aca="false">IF($C$6+14&gt;DaysPerYear,$C$6+14-DaysPerYear,$C$6+14)</f>
         <v>64</v>
       </c>
       <c r="K20" s="154" t="n">
@@ -5879,7 +5910,7 @@
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45"/>
       <c r="B21" s="160" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C21" s="163" t="n">
         <f aca="false">IFERROR(IF(ISBLANK(INDEX(Crops!$N$5:$N$22,MATCH($C$5,CropNames,0))),DefaultRipeMul,INDEX(Crops!$N$5:$N$22,MATCH($C$5,CropNames,0))),DefaultRipeMul)</f>
@@ -5889,10 +5920,10 @@
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
       <c r="G21" s="79" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="J21" s="153" t="n">
-        <f aca="false">IF($C$6+15&gt;108,$C$6+15-108,$C$6+15)</f>
+        <f aca="false">IF($C$6+15&gt;DaysPerYear,$C$6+15-DaysPerYear,$C$6+15)</f>
         <v>65</v>
       </c>
       <c r="K21" s="154" t="n">
@@ -5919,7 +5950,7 @@
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="38"/>
       <c r="B22" s="161" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C22" s="159" t="n">
         <f aca="false">IFERROR(IF(ISBLANK(INDEX(Crops!$O$5:$O$22,MATCH($C$5,CropNames,0))),DefaultStuntMul,INDEX(Crops!$O$5:$O$22,MATCH($C$5,CropNames,0))),DefaultStuntMul)</f>
@@ -5929,10 +5960,10 @@
       <c r="E22" s="38"/>
       <c r="F22" s="38"/>
       <c r="G22" s="76" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="J22" s="153" t="n">
-        <f aca="false">IF($C$6+16&gt;108,$C$6+16-108,$C$6+16)</f>
+        <f aca="false">IF($C$6+16&gt;DaysPerYear,$C$6+16-DaysPerYear,$C$6+16)</f>
         <v>66</v>
       </c>
       <c r="K22" s="154" t="n">
@@ -5958,7 +5989,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J23" s="153" t="n">
-        <f aca="false">IF($C$6+17&gt;108,$C$6+17-108,$C$6+17)</f>
+        <f aca="false">IF($C$6+17&gt;DaysPerYear,$C$6+17-DaysPerYear,$C$6+17)</f>
         <v>67</v>
       </c>
       <c r="K23" s="154" t="n">
@@ -5984,7 +6015,7 @@
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -5993,7 +6024,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="J24" s="153" t="n">
-        <f aca="false">IF($C$6+18&gt;108,$C$6+18-108,$C$6+18)</f>
+        <f aca="false">IF($C$6+18&gt;DaysPerYear,$C$6+18-DaysPerYear,$C$6+18)</f>
         <v>68</v>
       </c>
       <c r="K24" s="154" t="n">
@@ -6020,7 +6051,7 @@
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38"/>
       <c r="B25" s="161" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C25" s="164" t="n">
         <f aca="false">MAX(0.01,$C$9*100/70-0.143)^0.35</f>
@@ -6030,10 +6061,10 @@
       <c r="E25" s="38"/>
       <c r="F25" s="38"/>
       <c r="G25" s="76" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="J25" s="153" t="n">
-        <f aca="false">IF($C$6+19&gt;108,$C$6+19-108,$C$6+19)</f>
+        <f aca="false">IF($C$6+19&gt;DaysPerYear,$C$6+19-DaysPerYear,$C$6+19)</f>
         <v>69</v>
       </c>
       <c r="K25" s="154" t="n">
@@ -6060,7 +6091,7 @@
     <row r="26" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="45"/>
       <c r="B26" s="160" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C26" s="109" t="n">
         <f aca="false">IF($C$7&gt;75,1.1,IF($C$7&gt;50,1,IF($C$7&gt;35,0.9,IF($C$7&gt;20,0.6,IF($C$7&gt;5,0.3,0.1)))))</f>
@@ -6070,10 +6101,10 @@
       <c r="E26" s="45"/>
       <c r="F26" s="45"/>
       <c r="G26" s="79" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="J26" s="153" t="n">
-        <f aca="false">IF($C$6+20&gt;108,$C$6+20-108,$C$6+20)</f>
+        <f aca="false">IF($C$6+20&gt;DaysPerYear,$C$6+20-DaysPerYear,$C$6+20)</f>
         <v>70</v>
       </c>
       <c r="K26" s="154" t="n">
@@ -6100,7 +6131,7 @@
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="38"/>
       <c r="B27" s="161" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="C27" s="164" t="n">
         <f aca="false">$C$25*$C$26</f>
@@ -6110,10 +6141,10 @@
       <c r="E27" s="38"/>
       <c r="F27" s="38"/>
       <c r="G27" s="152" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="J27" s="153" t="n">
-        <f aca="false">IF($C$6+21&gt;108,$C$6+21-108,$C$6+21)</f>
+        <f aca="false">IF($C$6+21&gt;DaysPerYear,$C$6+21-DaysPerYear,$C$6+21)</f>
         <v>71</v>
       </c>
       <c r="K27" s="154" t="n">
@@ -6140,7 +6171,7 @@
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="45"/>
       <c r="B28" s="160" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="C28" s="165" t="n">
         <f aca="false">HoursPerDay*$C$15/MAX(1,$C$13-1)/$C$27/GrowthMul</f>
@@ -6150,10 +6181,10 @@
       <c r="E28" s="45"/>
       <c r="F28" s="45"/>
       <c r="G28" s="158" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="J28" s="153" t="n">
-        <f aca="false">IF($C$6+22&gt;108,$C$6+22-108,$C$6+22)</f>
+        <f aca="false">IF($C$6+22&gt;DaysPerYear,$C$6+22-DaysPerYear,$C$6+22)</f>
         <v>72</v>
       </c>
       <c r="K28" s="154" t="n">
@@ -6180,7 +6211,7 @@
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="38"/>
       <c r="B29" s="161" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C29" s="166" t="n">
         <f aca="false">$C$28*($C$13-1)</f>
@@ -6190,10 +6221,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="152" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="J29" s="153" t="n">
-        <f aca="false">IF($C$6+23&gt;108,$C$6+23-108,$C$6+23)</f>
+        <f aca="false">IF($C$6+23&gt;DaysPerYear,$C$6+23-DaysPerYear,$C$6+23)</f>
         <v>73</v>
       </c>
       <c r="K29" s="154" t="n">
@@ -6220,7 +6251,7 @@
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="45"/>
       <c r="B30" s="160" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="C30" s="165" t="n">
         <f aca="false">$C$29/HoursPerDay</f>
@@ -6231,7 +6262,7 @@
       <c r="F30" s="45"/>
       <c r="G30" s="45"/>
       <c r="J30" s="153" t="n">
-        <f aca="false">IF($C$6+24&gt;108,$C$6+24-108,$C$6+24)</f>
+        <f aca="false">IF($C$6+24&gt;DaysPerYear,$C$6+24-DaysPerYear,$C$6+24)</f>
         <v>74</v>
       </c>
       <c r="K30" s="154" t="n">
@@ -6257,7 +6288,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="J31" s="153" t="n">
-        <f aca="false">IF($C$6+25&gt;108,$C$6+25-108,$C$6+25)</f>
+        <f aca="false">IF($C$6+25&gt;DaysPerYear,$C$6+25-DaysPerYear,$C$6+25)</f>
         <v>75</v>
       </c>
       <c r="K31" s="154" t="n">
@@ -6283,7 +6314,7 @@
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5"/>
@@ -6292,7 +6323,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="J32" s="153" t="n">
-        <f aca="false">IF($C$6+26&gt;108,$C$6+26-108,$C$6+26)</f>
+        <f aca="false">IF($C$6+26&gt;DaysPerYear,$C$6+26-DaysPerYear,$C$6+26)</f>
         <v>76</v>
       </c>
       <c r="K32" s="154" t="n">
@@ -6319,7 +6350,7 @@
     <row r="33" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="38"/>
       <c r="B33" s="161" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="C33" s="94" t="str">
         <f aca="false">$C$6&amp;" → "&amp;($C$6+CEILING($C$30,1))</f>
@@ -6329,10 +6360,10 @@
       <c r="E33" s="38"/>
       <c r="F33" s="38"/>
       <c r="G33" s="152" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="J33" s="153" t="n">
-        <f aca="false">IF($C$6+27&gt;108,$C$6+27-108,$C$6+27)</f>
+        <f aca="false">IF($C$6+27&gt;DaysPerYear,$C$6+27-DaysPerYear,$C$6+27)</f>
         <v>77</v>
       </c>
       <c r="K33" s="154" t="n">
@@ -6359,20 +6390,20 @@
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="45"/>
       <c r="B34" s="160" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C34" s="165" t="n">
-        <f aca="true">IF($C$8,MIN(OFFSET(Climate!$H$5,$C$6-1,0,MIN(108-$C$6+1,CEILING($C$30,1)+1),1)),MIN(OFFSET(Climate!$E$5,$C$6-1,0,MIN(108-$C$6+1,CEILING($C$30,1)+1),1)))</f>
+        <f aca="true">IF($C$8,MIN(OFFSET(Climate!$H$5,$C$6-1,0,MIN(ClimateRows-$C$6+1,CEILING($C$30,1)+1),1)),MIN(OFFSET(Climate!$E$5,$C$6-1,0,MIN(ClimateRows-$C$6+1,CEILING($C$30,1)+1),1)))</f>
         <v>4.21</v>
       </c>
       <c r="D34" s="45"/>
       <c r="E34" s="45"/>
       <c r="F34" s="45"/>
       <c r="G34" s="158" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="J34" s="153" t="n">
-        <f aca="false">IF($C$6+28&gt;108,$C$6+28-108,$C$6+28)</f>
+        <f aca="false">IF($C$6+28&gt;DaysPerYear,$C$6+28-DaysPerYear,$C$6+28)</f>
         <v>78</v>
       </c>
       <c r="K34" s="154" t="n">
@@ -6399,10 +6430,10 @@
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="38"/>
       <c r="B35" s="161" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C35" s="166" t="n">
-        <f aca="true">IF($C$8,MAX(OFFSET(Climate!$I$5,$C$6-1,0,MIN(108-$C$6+1,CEILING($C$30,1)+1),1)),MAX(OFFSET(Climate!$F$5,$C$6-1,0,MIN(108-$C$6+1,CEILING($C$30,1)+1),1)))</f>
+        <f aca="true">IF($C$8,MAX(OFFSET(Climate!$I$5,$C$6-1,0,MIN(ClimateRows-$C$6+1,CEILING($C$30,1)+1),1)),MAX(OFFSET(Climate!$F$5,$C$6-1,0,MIN(ClimateRows-$C$6+1,CEILING($C$30,1)+1),1)))</f>
         <v>24.64</v>
       </c>
       <c r="D35" s="38"/>
@@ -6410,7 +6441,7 @@
       <c r="F35" s="38"/>
       <c r="G35" s="38"/>
       <c r="J35" s="153" t="n">
-        <f aca="false">IF($C$6+29&gt;108,$C$6+29-108,$C$6+29)</f>
+        <f aca="false">IF($C$6+29&gt;DaysPerYear,$C$6+29-DaysPerYear,$C$6+29)</f>
         <v>79</v>
       </c>
       <c r="K35" s="154" t="n">
@@ -6437,22 +6468,22 @@
     <row r="36" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="45"/>
       <c r="B36" s="160" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C36" s="165" t="n">
-        <f aca="true">IF($C$8,AVERAGE(OFFSET(Climate!$G$5,$C$6-1,0,MIN(108-$C$6+1,CEILING($C$30,1)+1),1)),AVERAGE(OFFSET(Climate!$D$5,$C$6-1,0,MIN(108-$C$6+1,CEILING($C$30,1)+1),1)))</f>
+        <f aca="true">IF($C$8,AVERAGE(OFFSET(Climate!$G$5,$C$6-1,0,MIN(ClimateRows-$C$6+1,CEILING($C$30,1)+1),1)),AVERAGE(OFFSET(Climate!$D$5,$C$6-1,0,MIN(ClimateRows-$C$6+1,CEILING($C$30,1)+1),1)))</f>
         <v>14.4227777777778</v>
       </c>
       <c r="D36" s="45"/>
       <c r="E36" s="45"/>
       <c r="F36" s="45"/>
       <c r="G36" s="158" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
@@ -6464,7 +6495,7 @@
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="38"/>
       <c r="B39" s="161" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C39" s="94" t="str">
         <f aca="false">IF($C$34&lt;$C$19,"YES. Stunt","no")</f>
@@ -6474,13 +6505,13 @@
       <c r="E39" s="38"/>
       <c r="F39" s="38"/>
       <c r="G39" s="152" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="45"/>
       <c r="B40" s="160" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C40" s="103" t="str">
         <f aca="false">IF($C$35&gt;$C$20,"YES. Stunt","no")</f>
@@ -6490,13 +6521,13 @@
       <c r="E40" s="45"/>
       <c r="F40" s="45"/>
       <c r="G40" s="158" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="38"/>
       <c r="B41" s="161" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C41" s="94" t="str">
         <f aca="false">IF($C$36&lt;=0,"STALLS. Avg ≤ 0","grows")</f>
@@ -6506,12 +6537,12 @@
       <c r="E41" s="38"/>
       <c r="F41" s="38"/>
       <c r="G41" s="152" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -6523,7 +6554,7 @@
     <row r="44" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="38"/>
       <c r="B44" s="161" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C44" s="100" t="n">
         <f aca="false">MAX(0,MIN(1,1+($C$36-TempThresh)*TempLoss))</f>
@@ -6533,13 +6564,13 @@
       <c r="E44" s="38"/>
       <c r="F44" s="38"/>
       <c r="G44" s="152" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="45"/>
       <c r="B45" s="160" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C45" s="165" t="n">
         <f aca="false">IF($C$44&lt;=0,"never",$C$30/$C$44)</f>
@@ -6549,13 +6580,13 @@
       <c r="E45" s="45"/>
       <c r="F45" s="45"/>
       <c r="G45" s="158" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="38"/>
       <c r="B46" s="161" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C46" s="94" t="n">
         <f aca="false">IFERROR(IF(ISNUMBER($C$45),$C$6+ROUND($C$45,0),"never"),"never")</f>
@@ -6565,12 +6596,12 @@
       <c r="E46" s="38"/>
       <c r="F46" s="38"/>
       <c r="G46" s="152" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -6581,7 +6612,7 @@
     </row>
     <row r="49" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="167" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C49" s="168" t="str">
         <f aca="false">IF($C$41="STALLS. Avg ≤ 0","STALLS",IF(AND($C$39="no",$C$40="no"),"HEALTHY",IF($C$39&lt;&gt;"no","DAMAGED (cold)","DAMAGED (heat)")))</f>
@@ -6591,7 +6622,7 @@
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="167" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C50" s="170" t="n">
         <f aca="false">IF($C$49="HEALTHY",1,IF($C$49="STALLS",0,$C$22))</f>
@@ -6600,7 +6631,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="171" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B52" s="171"/>
       <c r="C52" s="171"/>
@@ -6611,7 +6642,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="171" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="B53" s="171"/>
       <c r="C53" s="171"/>
@@ -6622,7 +6653,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="171" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B54" s="171"/>
       <c r="C54" s="171"/>
@@ -6711,7 +6742,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -6731,7 +6762,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -6751,7 +6782,7 @@
     </row>
     <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="172" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -6772,14 +6803,14 @@
     <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="63"/>
       <c r="B4" s="173" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C4" s="174" t="str">
         <f aca="false">CurrentDay&amp;" ("&amp;MOD(CurrentDay-1,DaysPerMonth)+1&amp;" "&amp;CHOOSE(INT((CurrentDay-1)/DaysPerMonth)+1,"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec")&amp;")"</f>
         <v>50 (5 Jun)</v>
       </c>
       <c r="D4" s="175" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="E4" s="175"/>
       <c r="F4" s="175"/>
@@ -6796,58 +6827,58 @@
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="T5" s="5" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="U5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="37" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="D6" s="37" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E6" s="37" t="s">
-        <v>554</v>
+        <v>560</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>556</v>
+        <v>562</v>
       </c>
       <c r="I6" s="37" t="s">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="K6" s="37" t="s">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="L6" s="37" t="s">
-        <v>560</v>
+        <v>566</v>
       </c>
       <c r="M6" s="37" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="N6" s="37" t="s">
-        <v>562</v>
+        <v>568</v>
       </c>
       <c r="O6" s="37" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="T6" s="176" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="U6" s="177" t="n">
         <f aca="false">COUNTIF(Plots!$M$7:$M$18,"growing")</f>
@@ -6857,7 +6888,7 @@
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="38"/>
       <c r="B7" s="94" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C7" s="178"/>
       <c r="D7" s="179" t="n">
@@ -6868,7 +6899,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="151" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G7" s="179" t="n">
         <v>50</v>
@@ -6895,22 +6926,22 @@
         <v>growing</v>
       </c>
       <c r="N7" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G7),ISBLANK($F7)),"",IF(MIN(OFFSET(Climate!$E$5,$G7-1,0,MIN($J7+1,108-$G7+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F7,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G7),ISBLANK($F7)),"",IF(MIN(OFFSET(Climate!$E$5,$G7-1,0,MIN($J7+1,ClimateRows-$G7+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F7,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O7" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G7),ISBLANK($F7)),"",IF(MAX(OFFSET(Climate!$F$5,$G7-1,0,MIN($J7+1,108-$G7+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F7,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G7),ISBLANK($F7)),"",IF(MAX(OFFSET(Climate!$F$5,$G7-1,0,MIN($J7+1,ClimateRows-$G7+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F7,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P7" s="178"/>
       <c r="R7" s="130" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="S7" s="130" t="s">
-        <v>564</v>
+        <v>570</v>
       </c>
       <c r="T7" s="183" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="U7" s="184" t="n">
         <f aca="false">COUNTIF(Plots!$M$7:$M$18,"ripening")</f>
@@ -6920,7 +6951,7 @@
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="45"/>
       <c r="B8" s="103" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C8" s="178"/>
       <c r="D8" s="181"/>
@@ -6952,23 +6983,23 @@
         <v>empty</v>
       </c>
       <c r="N8" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G8),ISBLANK($F8)),"",IF(MIN(OFFSET(Climate!$E$5,$G8-1,0,MIN($J8+1,108-$G8+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F8,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G8),ISBLANK($F8)),"",IF(MIN(OFFSET(Climate!$E$5,$G8-1,0,MIN($J8+1,ClimateRows-$G8+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F8,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O8" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G8),ISBLANK($F8)),"",IF(MAX(OFFSET(Climate!$F$5,$G8-1,0,MIN($J8+1,108-$G8+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F8,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G8),ISBLANK($F8)),"",IF(MAX(OFFSET(Climate!$F$5,$G8-1,0,MIN($J8+1,ClimateRows-$G8+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F8,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P8" s="178"/>
       <c r="R8" s="130" t="s">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="S8" s="130" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"growing")</f>
         <v>1</v>
       </c>
       <c r="T8" s="176" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="U8" s="177" t="n">
         <f aca="false">COUNTIF(Plots!$M$7:$M$18,"READY")</f>
@@ -6978,7 +7009,7 @@
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="38"/>
       <c r="B9" s="94" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C9" s="178"/>
       <c r="D9" s="181"/>
@@ -7010,23 +7041,23 @@
         <v>empty</v>
       </c>
       <c r="N9" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G9),ISBLANK($F9)),"",IF(MIN(OFFSET(Climate!$E$5,$G9-1,0,MIN($J9+1,108-$G9+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F9,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G9),ISBLANK($F9)),"",IF(MIN(OFFSET(Climate!$E$5,$G9-1,0,MIN($J9+1,ClimateRows-$G9+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F9,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O9" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G9),ISBLANK($F9)),"",IF(MAX(OFFSET(Climate!$F$5,$G9-1,0,MIN($J9+1,108-$G9+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F9,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G9),ISBLANK($F9)),"",IF(MAX(OFFSET(Climate!$F$5,$G9-1,0,MIN($J9+1,ClimateRows-$G9+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F9,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P9" s="178"/>
       <c r="R9" s="130" t="s">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="S9" s="130" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"ripening")</f>
         <v>0</v>
       </c>
       <c r="T9" s="183" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="U9" s="184" t="n">
         <f aca="false">COUNTIF(Plots!$M$7:$M$18,"empty")</f>
@@ -7036,7 +7067,7 @@
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="45"/>
       <c r="B10" s="103" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C10" s="178"/>
       <c r="D10" s="181"/>
@@ -7068,23 +7099,23 @@
         <v>empty</v>
       </c>
       <c r="N10" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G10),ISBLANK($F10)),"",IF(MIN(OFFSET(Climate!$E$5,$G10-1,0,MIN($J10+1,108-$G10+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F10,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G10),ISBLANK($F10)),"",IF(MIN(OFFSET(Climate!$E$5,$G10-1,0,MIN($J10+1,ClimateRows-$G10+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F10,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O10" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G10),ISBLANK($F10)),"",IF(MAX(OFFSET(Climate!$F$5,$G10-1,0,MIN($J10+1,108-$G10+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F10,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G10),ISBLANK($F10)),"",IF(MAX(OFFSET(Climate!$F$5,$G10-1,0,MIN($J10+1,ClimateRows-$G10+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F10,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P10" s="178"/>
       <c r="R10" s="130" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="S10" s="130" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"READY")</f>
         <v>0</v>
       </c>
       <c r="T10" s="176" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="U10" s="177" t="n">
         <f aca="false">COUNTIF(Plots!$M$7:$M$18,"unplanted")</f>
@@ -7094,7 +7125,7 @@
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="38"/>
       <c r="B11" s="94" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C11" s="178"/>
       <c r="D11" s="181"/>
@@ -7126,16 +7157,16 @@
         <v>empty</v>
       </c>
       <c r="N11" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G11),ISBLANK($F11)),"",IF(MIN(OFFSET(Climate!$E$5,$G11-1,0,MIN($J11+1,108-$G11+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F11,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G11),ISBLANK($F11)),"",IF(MIN(OFFSET(Climate!$E$5,$G11-1,0,MIN($J11+1,ClimateRows-$G11+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F11,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O11" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G11),ISBLANK($F11)),"",IF(MAX(OFFSET(Climate!$F$5,$G11-1,0,MIN($J11+1,108-$G11+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F11,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G11),ISBLANK($F11)),"",IF(MAX(OFFSET(Climate!$F$5,$G11-1,0,MIN($J11+1,ClimateRows-$G11+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F11,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P11" s="178"/>
       <c r="R11" s="130" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="S11" s="130" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"empty")</f>
@@ -7145,7 +7176,7 @@
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="45"/>
       <c r="B12" s="103" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C12" s="178"/>
       <c r="D12" s="181"/>
@@ -7177,16 +7208,16 @@
         <v>empty</v>
       </c>
       <c r="N12" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G12),ISBLANK($F12)),"",IF(MIN(OFFSET(Climate!$E$5,$G12-1,0,MIN($J12+1,108-$G12+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F12,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G12),ISBLANK($F12)),"",IF(MIN(OFFSET(Climate!$E$5,$G12-1,0,MIN($J12+1,ClimateRows-$G12+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F12,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O12" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G12),ISBLANK($F12)),"",IF(MAX(OFFSET(Climate!$F$5,$G12-1,0,MIN($J12+1,108-$G12+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F12,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G12),ISBLANK($F12)),"",IF(MAX(OFFSET(Climate!$F$5,$G12-1,0,MIN($J12+1,ClimateRows-$G12+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F12,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P12" s="178"/>
       <c r="R12" s="130" t="s">
-        <v>571</v>
+        <v>577</v>
       </c>
       <c r="S12" s="130" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"unplanted")</f>
@@ -7196,7 +7227,7 @@
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="38"/>
       <c r="B13" s="94" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C13" s="178"/>
       <c r="D13" s="181"/>
@@ -7228,11 +7259,11 @@
         <v>empty</v>
       </c>
       <c r="N13" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G13),ISBLANK($F13)),"",IF(MIN(OFFSET(Climate!$E$5,$G13-1,0,MIN($J13+1,108-$G13+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F13,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G13),ISBLANK($F13)),"",IF(MIN(OFFSET(Climate!$E$5,$G13-1,0,MIN($J13+1,ClimateRows-$G13+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F13,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O13" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G13),ISBLANK($F13)),"",IF(MAX(OFFSET(Climate!$F$5,$G13-1,0,MIN($J13+1,108-$G13+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F13,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G13),ISBLANK($F13)),"",IF(MAX(OFFSET(Climate!$F$5,$G13-1,0,MIN($J13+1,ClimateRows-$G13+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F13,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P13" s="178"/>
@@ -7240,7 +7271,7 @@
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="45"/>
       <c r="B14" s="103" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C14" s="178"/>
       <c r="D14" s="181"/>
@@ -7272,11 +7303,11 @@
         <v>empty</v>
       </c>
       <c r="N14" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G14),ISBLANK($F14)),"",IF(MIN(OFFSET(Climate!$E$5,$G14-1,0,MIN($J14+1,108-$G14+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F14,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G14),ISBLANK($F14)),"",IF(MIN(OFFSET(Climate!$E$5,$G14-1,0,MIN($J14+1,ClimateRows-$G14+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F14,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O14" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G14),ISBLANK($F14)),"",IF(MAX(OFFSET(Climate!$F$5,$G14-1,0,MIN($J14+1,108-$G14+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F14,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G14),ISBLANK($F14)),"",IF(MAX(OFFSET(Climate!$F$5,$G14-1,0,MIN($J14+1,ClimateRows-$G14+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F14,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P14" s="178"/>
@@ -7284,7 +7315,7 @@
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="38"/>
       <c r="B15" s="94" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C15" s="178"/>
       <c r="D15" s="181"/>
@@ -7316,11 +7347,11 @@
         <v>empty</v>
       </c>
       <c r="N15" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G15),ISBLANK($F15)),"",IF(MIN(OFFSET(Climate!$E$5,$G15-1,0,MIN($J15+1,108-$G15+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F15,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G15),ISBLANK($F15)),"",IF(MIN(OFFSET(Climate!$E$5,$G15-1,0,MIN($J15+1,ClimateRows-$G15+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F15,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O15" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G15),ISBLANK($F15)),"",IF(MAX(OFFSET(Climate!$F$5,$G15-1,0,MIN($J15+1,108-$G15+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F15,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G15),ISBLANK($F15)),"",IF(MAX(OFFSET(Climate!$F$5,$G15-1,0,MIN($J15+1,ClimateRows-$G15+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F15,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P15" s="178"/>
@@ -7328,7 +7359,7 @@
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="45"/>
       <c r="B16" s="103" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="C16" s="178"/>
       <c r="D16" s="181"/>
@@ -7360,11 +7391,11 @@
         <v>empty</v>
       </c>
       <c r="N16" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G16),ISBLANK($F16)),"",IF(MIN(OFFSET(Climate!$E$5,$G16-1,0,MIN($J16+1,108-$G16+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F16,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G16),ISBLANK($F16)),"",IF(MIN(OFFSET(Climate!$E$5,$G16-1,0,MIN($J16+1,ClimateRows-$G16+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F16,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O16" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G16),ISBLANK($F16)),"",IF(MAX(OFFSET(Climate!$F$5,$G16-1,0,MIN($J16+1,108-$G16+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F16,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G16),ISBLANK($F16)),"",IF(MAX(OFFSET(Climate!$F$5,$G16-1,0,MIN($J16+1,ClimateRows-$G16+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F16,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P16" s="178"/>
@@ -7372,7 +7403,7 @@
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="38"/>
       <c r="B17" s="94" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C17" s="178"/>
       <c r="D17" s="181"/>
@@ -7404,11 +7435,11 @@
         <v>empty</v>
       </c>
       <c r="N17" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G17),ISBLANK($F17)),"",IF(MIN(OFFSET(Climate!$E$5,$G17-1,0,MIN($J17+1,108-$G17+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F17,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G17),ISBLANK($F17)),"",IF(MIN(OFFSET(Climate!$E$5,$G17-1,0,MIN($J17+1,ClimateRows-$G17+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F17,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O17" s="182" t="str">
-        <f aca="true">IF(OR(ISBLANK($G17),ISBLANK($F17)),"",IF(MAX(OFFSET(Climate!$F$5,$G17-1,0,MIN($J17+1,108-$G17+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F17,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G17),ISBLANK($F17)),"",IF(MAX(OFFSET(Climate!$F$5,$G17-1,0,MIN($J17+1,ClimateRows-$G17+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F17,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P17" s="178"/>
@@ -7416,7 +7447,7 @@
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="45"/>
       <c r="B18" s="103" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C18" s="178"/>
       <c r="D18" s="181"/>
@@ -7448,18 +7479,18 @@
         <v>empty</v>
       </c>
       <c r="N18" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G18),ISBLANK($F18)),"",IF(MIN(OFFSET(Climate!$E$5,$G18-1,0,MIN($J18+1,108-$G18+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F18,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G18),ISBLANK($F18)),"",IF(MIN(OFFSET(Climate!$E$5,$G18-1,0,MIN($J18+1,ClimateRows-$G18+1),1))&lt;INDEX(Crops!$K$5:$K$22,MATCH($F18,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="O18" s="186" t="str">
-        <f aca="true">IF(OR(ISBLANK($G18),ISBLANK($F18)),"",IF(MAX(OFFSET(Climate!$F$5,$G18-1,0,MIN($J18+1,108-$G18+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F18,CropNames,0)),"!",""))</f>
+        <f aca="true">IF(OR(ISBLANK($G18),ISBLANK($F18)),"",IF(MAX(OFFSET(Climate!$F$5,$G18-1,0,MIN($J18+1,ClimateRows-$G18+1),1))&gt;INDEX(Crops!$M$5:$M$22,MATCH($F18,CropNames,0)),"!",""))</f>
         <v/>
       </c>
       <c r="P18" s="178"/>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5" t="s">
-        <v>580</v>
+        <v>586</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -7480,7 +7511,7 @@
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="66"/>
       <c r="B23" s="187" t="s">
-        <v>581</v>
+        <v>587</v>
       </c>
       <c r="C23" s="188" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"&lt;&gt;empty")-COUNTIF($M$7:$M$18,"unplanted")</f>
@@ -7503,7 +7534,7 @@
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="189" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
       <c r="C24" s="190" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"READY")</f>
@@ -7526,7 +7557,7 @@
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="66"/>
       <c r="B25" s="187" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
       <c r="C25" s="188" t="n">
         <f aca="false">COUNTIF($M$7:$M$18,"ripening")</f>
@@ -7549,7 +7580,7 @@
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="63"/>
       <c r="B26" s="189" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
       <c r="C26" s="190" t="n">
         <f aca="false">COUNTIF($N$7:$N$18,"!")</f>
@@ -7572,7 +7603,7 @@
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="66"/>
       <c r="B27" s="187" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
       <c r="C27" s="188" t="n">
         <f aca="false">COUNTIF($O$7:$O$18,"!")</f>
@@ -7696,7 +7727,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -7708,7 +7739,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -7720,7 +7751,7 @@
     </row>
     <row r="3" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="172" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="B3" s="172"/>
       <c r="C3" s="172"/>
@@ -7732,34 +7763,34 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="37" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="I5" s="191" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="38"/>
       <c r="B6" s="94" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="185"/>
       <c r="D6" s="180" t="str">
@@ -7780,7 +7811,7 @@
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="45"/>
       <c r="B7" s="103" t="s">
-        <v>566</v>
+        <v>572</v>
       </c>
       <c r="C7" s="185"/>
       <c r="D7" s="156" t="str">
@@ -7801,7 +7832,7 @@
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="38"/>
       <c r="B8" s="94" t="s">
-        <v>568</v>
+        <v>574</v>
       </c>
       <c r="C8" s="185"/>
       <c r="D8" s="180" t="str">
@@ -7822,7 +7853,7 @@
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="45"/>
       <c r="B9" s="103" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="C9" s="185"/>
       <c r="D9" s="156" t="str">
@@ -7843,7 +7874,7 @@
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="38"/>
       <c r="B10" s="94" t="s">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="C10" s="185"/>
       <c r="D10" s="180" t="str">
@@ -7864,7 +7895,7 @@
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="45"/>
       <c r="B11" s="103" t="s">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="C11" s="185"/>
       <c r="D11" s="156" t="str">
@@ -7885,7 +7916,7 @@
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="38"/>
       <c r="B12" s="94" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="C12" s="185"/>
       <c r="D12" s="180" t="str">
@@ -7906,7 +7937,7 @@
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="45"/>
       <c r="B13" s="103" t="s">
-        <v>575</v>
+        <v>581</v>
       </c>
       <c r="C13" s="185"/>
       <c r="D13" s="156" t="str">
@@ -7927,7 +7958,7 @@
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="38"/>
       <c r="B14" s="94" t="s">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="C14" s="185"/>
       <c r="D14" s="180" t="str">
@@ -7948,7 +7979,7 @@
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="45"/>
       <c r="B15" s="103" t="s">
-        <v>577</v>
+        <v>583</v>
       </c>
       <c r="C15" s="185"/>
       <c r="D15" s="156" t="str">
@@ -7969,7 +8000,7 @@
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38"/>
       <c r="B16" s="94" t="s">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C16" s="185"/>
       <c r="D16" s="180" t="str">
@@ -7990,7 +8021,7 @@
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="45"/>
       <c r="B17" s="103" t="s">
-        <v>579</v>
+        <v>585</v>
       </c>
       <c r="C17" s="185"/>
       <c r="D17" s="156" t="str">
@@ -8010,7 +8041,7 @@
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -8022,10 +8053,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="128" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="C21" s="192" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="D21" s="192"/>
       <c r="E21" s="192"/>
@@ -8035,10 +8066,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="128" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="C22" s="192" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="D22" s="192"/>
       <c r="E22" s="192"/>
@@ -8048,10 +8079,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="128" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
       <c r="C23" s="192" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
       <c r="D23" s="192"/>
       <c r="E23" s="192"/>
@@ -8118,7 +8149,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>604</v>
+        <v>610</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8131,7 +8162,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -8155,28 +8186,28 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="37" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8659,7 +8690,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>609</v>
+        <v>615</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -8671,7 +8702,7 @@
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>610</v>
+        <v>616</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -8679,186 +8710,186 @@
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="38"/>
       <c r="B4" s="199" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C4" s="200" t="s">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="D4" s="201"/>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="45"/>
       <c r="B5" s="202" t="s">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="C5" s="203" t="s">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="D5" s="201"/>
     </row>
     <row r="6" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="38"/>
       <c r="B6" s="199" t="s">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="C6" s="200" t="s">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="D6" s="201"/>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="45"/>
       <c r="B7" s="202" t="s">
-        <v>616</v>
+        <v>622</v>
       </c>
       <c r="C7" s="203" t="s">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="D7" s="201"/>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="38"/>
       <c r="B8" s="199" t="s">
-        <v>618</v>
+        <v>624</v>
       </c>
       <c r="C8" s="200" t="s">
-        <v>619</v>
+        <v>625</v>
       </c>
       <c r="D8" s="201"/>
     </row>
     <row r="9" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="45"/>
       <c r="B9" s="202" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="C9" s="203" t="s">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="D9" s="201"/>
     </row>
     <row r="10" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="38"/>
       <c r="B10" s="199" t="s">
-        <v>622</v>
+        <v>628</v>
       </c>
       <c r="C10" s="200" t="s">
-        <v>623</v>
+        <v>629</v>
       </c>
       <c r="D10" s="201"/>
     </row>
     <row r="11" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="45"/>
       <c r="B11" s="202" t="s">
-        <v>624</v>
+        <v>630</v>
       </c>
       <c r="C11" s="203" t="s">
-        <v>625</v>
+        <v>631</v>
       </c>
       <c r="D11" s="201"/>
     </row>
     <row r="12" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="38"/>
       <c r="B12" s="199" t="s">
-        <v>626</v>
+        <v>632</v>
       </c>
       <c r="C12" s="200" t="s">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="D12" s="201"/>
     </row>
     <row r="13" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="45"/>
       <c r="B13" s="202" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C13" s="203" t="s">
-        <v>628</v>
+        <v>634</v>
       </c>
       <c r="D13" s="201"/>
     </row>
     <row r="14" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="38"/>
       <c r="B14" s="199" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C14" s="200" t="s">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="D14" s="201"/>
     </row>
     <row r="15" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="45"/>
       <c r="B15" s="202" t="s">
-        <v>630</v>
+        <v>636</v>
       </c>
       <c r="C15" s="203" t="s">
-        <v>631</v>
+        <v>637</v>
       </c>
       <c r="D15" s="201"/>
     </row>
     <row r="16" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38"/>
       <c r="B16" s="199" t="s">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="C16" s="200" t="s">
-        <v>633</v>
+        <v>639</v>
       </c>
       <c r="D16" s="201"/>
     </row>
     <row r="17" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="45"/>
       <c r="B17" s="202" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C17" s="203" t="s">
-        <v>635</v>
+        <v>641</v>
       </c>
       <c r="D17" s="201"/>
     </row>
     <row r="18" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38"/>
       <c r="B18" s="199" t="s">
-        <v>636</v>
+        <v>642</v>
       </c>
       <c r="C18" s="200" t="s">
-        <v>637</v>
+        <v>643</v>
       </c>
       <c r="D18" s="201"/>
     </row>
     <row r="19" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="45"/>
       <c r="B19" s="202" t="s">
-        <v>638</v>
+        <v>644</v>
       </c>
       <c r="C19" s="203" t="s">
-        <v>639</v>
+        <v>645</v>
       </c>
       <c r="D19" s="201"/>
     </row>
     <row r="20" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="38"/>
       <c r="B20" s="199" t="s">
-        <v>640</v>
+        <v>646</v>
       </c>
       <c r="C20" s="200" t="s">
-        <v>641</v>
+        <v>647</v>
       </c>
       <c r="D20" s="201"/>
     </row>
     <row r="21" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="45"/>
       <c r="B21" s="202" t="s">
-        <v>642</v>
+        <v>648</v>
       </c>
       <c r="C21" s="203" t="s">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D21" s="201"/>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
@@ -8866,135 +8897,135 @@
     <row r="25" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="45"/>
       <c r="B25" s="204" t="s">
-        <v>645</v>
+        <v>651</v>
       </c>
       <c r="C25" s="118" t="s">
-        <v>646</v>
+        <v>652</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="38"/>
       <c r="B26" s="199" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C26" s="200" t="s">
-        <v>647</v>
+        <v>653</v>
       </c>
       <c r="D26" s="201"/>
     </row>
     <row r="27" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="45"/>
       <c r="B27" s="202" t="s">
-        <v>648</v>
+        <v>654</v>
       </c>
       <c r="C27" s="203" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="D27" s="201"/>
     </row>
     <row r="28" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="38"/>
       <c r="B28" s="199" t="s">
-        <v>620</v>
+        <v>626</v>
       </c>
       <c r="C28" s="200" t="s">
-        <v>650</v>
+        <v>656</v>
       </c>
       <c r="D28" s="201"/>
     </row>
     <row r="29" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="45"/>
       <c r="B29" s="202" t="s">
-        <v>651</v>
+        <v>657</v>
       </c>
       <c r="C29" s="203" t="s">
-        <v>652</v>
+        <v>658</v>
       </c>
       <c r="D29" s="201"/>
     </row>
     <row r="30" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="38"/>
       <c r="B30" s="199" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C30" s="200" t="s">
-        <v>653</v>
+        <v>659</v>
       </c>
       <c r="D30" s="201"/>
     </row>
     <row r="31" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="45"/>
       <c r="B31" s="202" t="s">
-        <v>654</v>
+        <v>660</v>
       </c>
       <c r="C31" s="203" t="s">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="D31" s="201"/>
     </row>
     <row r="32" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="38"/>
       <c r="B32" s="199" t="s">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="C32" s="200" t="s">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="D32" s="201"/>
     </row>
     <row r="33" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="45"/>
       <c r="B33" s="202" t="s">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="C33" s="203" t="s">
-        <v>659</v>
+        <v>665</v>
       </c>
       <c r="D33" s="201"/>
     </row>
     <row r="34" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="38"/>
       <c r="B34" s="199" t="s">
-        <v>660</v>
+        <v>666</v>
       </c>
       <c r="C34" s="200" t="s">
-        <v>661</v>
+        <v>667</v>
       </c>
       <c r="D34" s="201"/>
     </row>
     <row r="35" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="45"/>
       <c r="B35" s="202" t="s">
-        <v>634</v>
+        <v>640</v>
       </c>
       <c r="C35" s="203" t="s">
-        <v>662</v>
+        <v>668</v>
       </c>
       <c r="D35" s="201"/>
     </row>
     <row r="36" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="38"/>
       <c r="B36" s="199" t="s">
-        <v>663</v>
+        <v>669</v>
       </c>
       <c r="C36" s="200" t="s">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="D36" s="201"/>
     </row>
     <row r="37" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="45"/>
       <c r="B37" s="202" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C37" s="203" t="s">
-        <v>665</v>
+        <v>671</v>
       </c>
       <c r="D37" s="201"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -9002,75 +9033,75 @@
     <row r="42" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="38"/>
       <c r="B42" s="205" t="s">
-        <v>666</v>
+        <v>672</v>
       </c>
       <c r="C42" s="200" t="s">
-        <v>667</v>
+        <v>673</v>
       </c>
       <c r="D42" s="201"/>
     </row>
     <row r="43" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="45"/>
       <c r="B43" s="206" t="s">
-        <v>668</v>
+        <v>674</v>
       </c>
       <c r="C43" s="203" t="s">
-        <v>669</v>
+        <v>675</v>
       </c>
       <c r="D43" s="201"/>
     </row>
     <row r="44" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="38"/>
       <c r="B44" s="205" t="s">
-        <v>670</v>
+        <v>676</v>
       </c>
       <c r="C44" s="200" t="s">
-        <v>671</v>
+        <v>677</v>
       </c>
       <c r="D44" s="201"/>
     </row>
     <row r="45" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="45"/>
       <c r="B45" s="206" t="s">
-        <v>672</v>
+        <v>678</v>
       </c>
       <c r="C45" s="203" t="s">
-        <v>673</v>
+        <v>679</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="38"/>
       <c r="B46" s="205" t="s">
-        <v>674</v>
+        <v>680</v>
       </c>
       <c r="C46" s="200" t="s">
-        <v>675</v>
+        <v>681</v>
       </c>
       <c r="D46" s="201"/>
     </row>
     <row r="47" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="45"/>
       <c r="B47" s="206" t="s">
-        <v>676</v>
+        <v>682</v>
       </c>
       <c r="C47" s="203" t="s">
-        <v>677</v>
+        <v>683</v>
       </c>
       <c r="D47" s="201"/>
     </row>
     <row r="48" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="38"/>
       <c r="B48" s="205" t="s">
-        <v>678</v>
+        <v>684</v>
       </c>
       <c r="C48" s="200" t="s">
-        <v>679</v>
+        <v>685</v>
       </c>
       <c r="D48" s="201"/>
     </row>
     <row r="50" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5" t="s">
-        <v>680</v>
+        <v>686</v>
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
@@ -9079,7 +9110,7 @@
     <row r="51" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="207"/>
       <c r="B51" s="208" t="s">
-        <v>681</v>
+        <v>687</v>
       </c>
       <c r="C51" s="208"/>
       <c r="D51" s="208"/>
@@ -9087,106 +9118,106 @@
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="207"/>
       <c r="B52" s="37" t="s">
-        <v>682</v>
+        <v>688</v>
       </c>
       <c r="C52" s="37" t="s">
-        <v>683</v>
+        <v>689</v>
       </c>
       <c r="D52" s="37" t="s">
-        <v>561</v>
+        <v>567</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="207"/>
       <c r="B53" s="209" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="C53" s="210" t="s">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="D53" s="211" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="207"/>
       <c r="B54" s="212" t="s">
-        <v>687</v>
+        <v>693</v>
       </c>
       <c r="C54" s="213" t="s">
-        <v>688</v>
+        <v>694</v>
       </c>
       <c r="D54" s="211" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="207"/>
       <c r="B55" s="209" t="s">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="C55" s="210" t="s">
-        <v>690</v>
+        <v>696</v>
       </c>
       <c r="D55" s="211" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="207"/>
       <c r="B56" s="214" t="s">
-        <v>691</v>
+        <v>697</v>
       </c>
       <c r="C56" s="215" t="s">
-        <v>692</v>
+        <v>698</v>
       </c>
       <c r="D56" s="216" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="207"/>
       <c r="B57" s="217" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="C57" s="218" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="D57" s="219" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="207"/>
       <c r="B58" s="214" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="C58" s="215" t="s">
-        <v>697</v>
+        <v>703</v>
       </c>
       <c r="D58" s="220" t="s">
-        <v>698</v>
+        <v>704</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="207"/>
       <c r="B59" s="217" t="s">
-        <v>699</v>
+        <v>705</v>
       </c>
       <c r="C59" s="218" t="s">
-        <v>700</v>
+        <v>706</v>
       </c>
       <c r="D59" s="219" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="61.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="207"/>
       <c r="B60" s="221" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="C60" s="222" t="s">
-        <v>702</v>
+        <v>708</v>
       </c>
       <c r="D60" s="222"/>
     </row>
@@ -9198,7 +9229,7 @@
     </row>
     <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="223" t="s">
-        <v>703</v>
+        <v>709</v>
       </c>
       <c r="B62" s="223"/>
       <c r="C62" s="223"/>
@@ -9206,7 +9237,7 @@
     </row>
     <row r="63" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="224" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="B63" s="224"/>
       <c r="C63" s="224"/>
@@ -9214,64 +9245,64 @@
     </row>
     <row r="65" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B65" s="225" t="s">
-        <v>705</v>
+        <v>711</v>
       </c>
       <c r="C65" s="226" t="s">
-        <v>706</v>
+        <v>712</v>
       </c>
       <c r="D65" s="227" t="s">
-        <v>707</v>
+        <v>713</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="228"/>
       <c r="B66" s="229" t="s">
-        <v>708</v>
+        <v>714</v>
       </c>
       <c r="C66" s="230" t="s">
-        <v>709</v>
+        <v>715</v>
       </c>
       <c r="D66" s="231" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B67" s="225" t="s">
-        <v>711</v>
+        <v>717</v>
       </c>
       <c r="C67" s="226" t="s">
-        <v>712</v>
+        <v>718</v>
       </c>
       <c r="D67" s="227" t="s">
-        <v>713</v>
+        <v>719</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="228"/>
       <c r="B68" s="229" t="s">
-        <v>714</v>
+        <v>720</v>
       </c>
       <c r="C68" s="230" t="s">
-        <v>715</v>
+        <v>721</v>
       </c>
       <c r="D68" s="231" t="s">
-        <v>716</v>
+        <v>722</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B69" s="225" t="s">
-        <v>717</v>
+        <v>723</v>
       </c>
       <c r="C69" s="226" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="D69" s="227" t="s">
-        <v>719</v>
+        <v>725</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="232" t="s">
-        <v>720</v>
+        <v>726</v>
       </c>
       <c r="B71" s="232"/>
       <c r="C71" s="232"/>
@@ -9279,30 +9310,30 @@
     </row>
     <row r="72" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="225" t="s">
-        <v>721</v>
+        <v>727</v>
       </c>
       <c r="C72" s="226" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
       <c r="D72" s="227" t="s">
-        <v>723</v>
+        <v>729</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="55.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="228"/>
       <c r="B73" s="229" t="s">
-        <v>724</v>
+        <v>730</v>
       </c>
       <c r="C73" s="230" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="D73" s="231" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="233" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="B75" s="233"/>
       <c r="C75" s="233"/>
@@ -9310,7 +9341,7 @@
     </row>
     <row r="77" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="223" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="B77" s="223"/>
       <c r="C77" s="223"/>
@@ -9318,7 +9349,7 @@
     </row>
     <row r="78" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="224" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="B78" s="224"/>
       <c r="C78" s="224"/>
@@ -9326,66 +9357,66 @@
     </row>
     <row r="80" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B80" s="225" t="s">
-        <v>730</v>
+        <v>736</v>
       </c>
       <c r="C80" s="226" t="s">
-        <v>731</v>
+        <v>737</v>
       </c>
       <c r="D80" s="227" t="s">
-        <v>732</v>
+        <v>738</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="234"/>
       <c r="B81" s="235" t="s">
-        <v>733</v>
+        <v>739</v>
       </c>
       <c r="C81" s="236" t="s">
-        <v>734</v>
+        <v>740</v>
       </c>
       <c r="D81" s="237" t="s">
-        <v>735</v>
+        <v>741</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="234"/>
       <c r="B82" s="235" t="s">
-        <v>736</v>
+        <v>742</v>
       </c>
       <c r="C82" s="236" t="s">
-        <v>737</v>
+        <v>743</v>
       </c>
       <c r="D82" s="237" t="s">
-        <v>738</v>
+        <v>744</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="228"/>
       <c r="B83" s="229" t="s">
-        <v>739</v>
+        <v>745</v>
       </c>
       <c r="C83" s="230" t="s">
-        <v>740</v>
+        <v>746</v>
       </c>
       <c r="D83" s="231" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="234"/>
       <c r="B84" s="235" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="C84" s="236" t="s">
-        <v>743</v>
+        <v>749</v>
       </c>
       <c r="D84" s="237" t="s">
-        <v>744</v>
+        <v>750</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="224" t="s">
-        <v>745</v>
+        <v>751</v>
       </c>
       <c r="B86" s="224"/>
       <c r="C86" s="224"/>
@@ -9439,7 +9470,7 @@
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="20"/>
       <c r="B1" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -9457,7 +9488,7 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="20"/>
       <c r="B2" s="3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -9491,7 +9522,7 @@
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="21"/>
       <c r="B5" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -9508,13 +9539,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="22" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E7" s="24"/>
       <c r="F7" s="24"/>
@@ -9529,13 +9560,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="22" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E8" s="24"/>
       <c r="F8" s="24"/>
@@ -9550,14 +9581,14 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="22" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">CurrentDay</f>
         <v>50</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E9" s="24"/>
       <c r="F9" s="24"/>
@@ -9572,14 +9603,14 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">IF($C$7="Linked to Plots",INDEX(Plots!$D$7:$D$18,MATCH($C$8,Plots!$B$7:$B$18,0)),65)</f>
         <v>65</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E10" s="24"/>
       <c r="F10" s="24"/>
@@ -9594,14 +9625,14 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="22" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" s="26" t="b">
         <f aca="false">IF($C$7="Linked to Plots",INDEX(Plots!$E$7:$E$18,MATCH($C$8,Plots!$B$7:$B$18,0)),FALSE())</f>
         <v>0</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E11" s="24"/>
       <c r="F11" s="24"/>
@@ -9616,14 +9647,14 @@
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="22" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C12" s="26" t="b">
         <f aca="false">HasPerk</f>
         <v>1</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E12" s="27"/>
       <c r="F12" s="27"/>
@@ -9638,14 +9669,14 @@
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="22" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C13" s="26" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E13" s="24"/>
       <c r="F13" s="24"/>
@@ -9660,10 +9691,10 @@
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="22" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D14" s="28" t="str">
         <f aca="false">IF($C$14="None","(no fertilizer)","+"&amp;IFERROR(VLOOKUP($C$14,Fertilizers!$B$6:$E$9,2,FALSE()),0)&amp;"N · +"&amp;IFERROR(VLOOKUP($C$14,Fertilizers!$B$6:$E$9,3,FALSE()),0)&amp;"P · +"&amp;IFERROR(VLOOKUP($C$14,Fertilizers!$B$6:$E$9,4,FALSE()),0)&amp;"K to slow-release pool")</f>
@@ -9674,7 +9705,7 @@
       <c r="G14" s="28"/>
       <c r="H14" s="28"/>
       <c r="I14" s="29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="J14" s="29"/>
       <c r="K14" s="29"/>
@@ -9684,7 +9715,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="30" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
@@ -9701,16 +9732,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="31" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J16" s="29"/>
       <c r="K16" s="29"/>
@@ -9734,7 +9765,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="22" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C18" s="25" t="n">
         <v>0</v>
@@ -9746,7 +9777,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="29" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J18" s="29"/>
       <c r="K18" s="29"/>
@@ -9757,7 +9788,7 @@
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="21"/>
       <c r="B19" s="5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -9774,7 +9805,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="22" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C21" s="32" t="str">
         <f aca="false">"Day "&amp;$C$9&amp;" ("&amp;MOD($C$9-1,DaysPerMonth)+1&amp;" "&amp;CHOOSE(INT(($C$9-1)/DaysPerMonth)+1,"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep","Oct","Nov","Dec")&amp;")"</f>
@@ -9785,7 +9816,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="22" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C22" s="33" t="str">
         <f aca="false">ROUND(IF($C$11,INDEX(Climate!$G$5:$G$112,$C$9),INDEX(Climate!$D$5:$D$112,$C$9)),1)&amp;"°C avg"</f>
@@ -9800,7 +9831,7 @@
         <v>22.8°C max</v>
       </c>
       <c r="F22" s="29" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G22" s="29"/>
       <c r="H22" s="29"/>
@@ -9813,7 +9844,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C23" s="34" t="str">
         <f aca="false">IF($C$9&gt;=SeasonEndDay,0,SeasonEndDay-$C$9)&amp;" days"</f>
@@ -9836,7 +9867,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="22" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C24" s="34" t="str">
         <f aca="false">IF(MIN($C$17,$E$17,$G$17)=$C$17,"N",IF(MIN($C$17,$E$17,$G$17)=$E$17,"P","K"))&amp;" ("&amp;MIN($C$17,$E$17,$G$17)&amp;")"</f>
@@ -9859,7 +9890,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="22" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C25" s="36" t="str">
         <f aca="false">IF($C$9&gt;SeasonEndDay,"Season has already ended. No outdoor planting until day 34",IF(SeasonEndDay-$C$9&lt;10,"Less than 10 days left. Only fast crops will finish",IF(SeasonEndDay-$C$9&lt;25,"Mid-late season. Pick fast/medium crops","Plenty of season left. Many options viable")))</f>
@@ -9880,7 +9911,7 @@
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="21"/>
       <c r="B27" s="5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -9897,53 +9928,53 @@
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="37" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D29" s="37" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E29" s="37" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G29" s="37" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="H29" s="37" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J29" s="37" t="s">
         <v>34</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="L29" s="37" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="38"/>
       <c r="B30" s="39" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C30" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Rye",CropNames,0))</f>
         <v>16.02</v>
       </c>
       <c r="D30" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C30,0)&gt;108,ROUND($C$9+$C30-108,0),ROUND($C$9+$C30,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C30,0)&gt;DaysPerYear,ROUND($C$9+$C30-DaysPerYear,0),ROUND($C$9+$C30,0))</f>
         <v>50→66</v>
       </c>
       <c r="E30" s="42" t="n">
@@ -9951,11 +9982,11 @@
         <v>18</v>
       </c>
       <c r="F30" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C30,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C30,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C30-108,0))))),IF(ROUND($C$9+$C30,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C30,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C30-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C30,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C30,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C30-DaysPerYear,0))))),IF(ROUND($C$9+$C30,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C30,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C30-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G30" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C30,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C30,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C30-108,0))))),IF(ROUND($C$9+$C30,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C30,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C30-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C30,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C30,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C30-DaysPerYear,0))))),IF(ROUND($C$9+$C30,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C30,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C30-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H30" s="43" t="str">
@@ -9987,14 +10018,14 @@
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="45"/>
       <c r="B31" s="46" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C31" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Carrot",CropNames,0))</f>
         <v>9.27</v>
       </c>
       <c r="D31" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C31,0)&gt;108,ROUND($C$9+$C31-108,0),ROUND($C$9+$C31,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C31,0)&gt;DaysPerYear,ROUND($C$9+$C31-DaysPerYear,0),ROUND($C$9+$C31,0))</f>
         <v>50→59</v>
       </c>
       <c r="E31" s="49" t="n">
@@ -10002,11 +10033,11 @@
         <v>25</v>
       </c>
       <c r="F31" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C31,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C31,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C31-108,0))))),IF(ROUND($C$9+$C31,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C31,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C31-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C31,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C31,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C31-DaysPerYear,0))))),IF(ROUND($C$9+$C31,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C31,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C31-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G31" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C31,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C31,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C31-108,0))))),IF(ROUND($C$9+$C31,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C31,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C31-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C31,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C31,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C31-DaysPerYear,0))))),IF(ROUND($C$9+$C31,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C31,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C31-DaysPerYear,0))))))</f>
         <v>24.07</v>
       </c>
       <c r="H31" s="50" t="str">
@@ -10038,14 +10069,14 @@
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="38"/>
       <c r="B32" s="39" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C32" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Parsnip",CropNames,0))</f>
         <v>15.75</v>
       </c>
       <c r="D32" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C32,0)&gt;108,ROUND($C$9+$C32-108,0),ROUND($C$9+$C32,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C32,0)&gt;DaysPerYear,ROUND($C$9+$C32-DaysPerYear,0),ROUND($C$9+$C32,0))</f>
         <v>50→66</v>
       </c>
       <c r="E32" s="42" t="n">
@@ -10053,11 +10084,11 @@
         <v>18</v>
       </c>
       <c r="F32" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C32,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C32,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C32-108,0))))),IF(ROUND($C$9+$C32,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C32,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C32-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C32,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C32,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C32-DaysPerYear,0))))),IF(ROUND($C$9+$C32,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C32,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C32-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G32" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C32,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C32,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C32-108,0))))),IF(ROUND($C$9+$C32,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C32,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C32-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C32,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C32,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C32-DaysPerYear,0))))),IF(ROUND($C$9+$C32,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C32,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C32-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H32" s="43" t="str">
@@ -10089,14 +10120,14 @@
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="45"/>
       <c r="B33" s="46" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C33" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Fennel",CropNames,0))</f>
         <v>24.03</v>
       </c>
       <c r="D33" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C33,0)&gt;108,ROUND($C$9+$C33-108,0),ROUND($C$9+$C33,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C33,0)&gt;DaysPerYear,ROUND($C$9+$C33-DaysPerYear,0),ROUND($C$9+$C33,0))</f>
         <v>50→74</v>
       </c>
       <c r="E33" s="49" t="n">
@@ -10104,11 +10135,11 @@
         <v>10</v>
       </c>
       <c r="F33" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C33,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C33,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C33-108,0))))),IF(ROUND($C$9+$C33,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C33,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C33-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C33,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C33,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C33-DaysPerYear,0))))),IF(ROUND($C$9+$C33,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C33,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C33-DaysPerYear,0))))))</f>
         <v>1.96</v>
       </c>
       <c r="G33" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C33,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C33,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C33-108,0))))),IF(ROUND($C$9+$C33,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C33,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C33-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C33,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C33,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C33-DaysPerYear,0))))),IF(ROUND($C$9+$C33,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C33,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C33-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H33" s="50" t="str">
@@ -10140,14 +10171,14 @@
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="38"/>
       <c r="B34" s="39" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C34" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Licorice",CropNames,0))</f>
         <v>24.03</v>
       </c>
       <c r="D34" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C34,0)&gt;108,ROUND($C$9+$C34-108,0),ROUND($C$9+$C34,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C34,0)&gt;DaysPerYear,ROUND($C$9+$C34-DaysPerYear,0),ROUND($C$9+$C34,0))</f>
         <v>50→74</v>
       </c>
       <c r="E34" s="42" t="n">
@@ -10155,11 +10186,11 @@
         <v>10</v>
       </c>
       <c r="F34" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C34,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C34,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C34-108,0))))),IF(ROUND($C$9+$C34,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C34,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C34-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C34,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C34,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C34-DaysPerYear,0))))),IF(ROUND($C$9+$C34,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C34,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C34-DaysPerYear,0))))))</f>
         <v>1.96</v>
       </c>
       <c r="G34" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C34,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C34,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C34-108,0))))),IF(ROUND($C$9+$C34,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C34,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C34-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C34,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C34,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C34-DaysPerYear,0))))),IF(ROUND($C$9+$C34,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C34,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C34-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H34" s="43" t="str">
@@ -10191,14 +10222,14 @@
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="45"/>
       <c r="B35" s="46" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C35" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Onion",CropNames,0))</f>
         <v>13.86</v>
       </c>
       <c r="D35" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C35,0)&gt;108,ROUND($C$9+$C35-108,0),ROUND($C$9+$C35,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C35,0)&gt;DaysPerYear,ROUND($C$9+$C35-DaysPerYear,0),ROUND($C$9+$C35,0))</f>
         <v>50→64</v>
       </c>
       <c r="E35" s="49" t="n">
@@ -10206,11 +10237,11 @@
         <v>20</v>
       </c>
       <c r="F35" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C35,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C35,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C35-108,0))))),IF(ROUND($C$9+$C35,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C35,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C35-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C35,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C35,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C35-DaysPerYear,0))))),IF(ROUND($C$9+$C35,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C35,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C35-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G35" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C35,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C35,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C35-108,0))))),IF(ROUND($C$9+$C35,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C35,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C35-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C35,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C35,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C35-DaysPerYear,0))))),IF(ROUND($C$9+$C35,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C35,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C35-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H35" s="50" t="str">
@@ -10242,14 +10273,14 @@
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="38"/>
       <c r="B36" s="39" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C36" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Turnip",CropNames,0))</f>
         <v>7.2</v>
       </c>
       <c r="D36" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C36,0)&gt;108,ROUND($C$9+$C36-108,0),ROUND($C$9+$C36,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C36,0)&gt;DaysPerYear,ROUND($C$9+$C36-DaysPerYear,0),ROUND($C$9+$C36,0))</f>
         <v>50→57</v>
       </c>
       <c r="E36" s="42" t="n">
@@ -10257,11 +10288,11 @@
         <v>27</v>
       </c>
       <c r="F36" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C36,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C36,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C36-108,0))))),IF(ROUND($C$9+$C36,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C36,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C36-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C36,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C36,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C36-DaysPerYear,0))))),IF(ROUND($C$9+$C36,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C36,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C36-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G36" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C36,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C36,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C36-108,0))))),IF(ROUND($C$9+$C36,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C36,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C36-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C36,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C36,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C36-DaysPerYear,0))))),IF(ROUND($C$9+$C36,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C36,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C36-DaysPerYear,0))))))</f>
         <v>24.07</v>
       </c>
       <c r="H36" s="43" t="str">
@@ -10293,14 +10324,14 @@
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="45"/>
       <c r="B37" s="46" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C37" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Cabbage",CropNames,0))</f>
         <v>12.375</v>
       </c>
       <c r="D37" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C37,0)&gt;108,ROUND($C$9+$C37-108,0),ROUND($C$9+$C37,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C37,0)&gt;DaysPerYear,ROUND($C$9+$C37-DaysPerYear,0),ROUND($C$9+$C37,0))</f>
         <v>50→62</v>
       </c>
       <c r="E37" s="49" t="n">
@@ -10308,11 +10339,11 @@
         <v>22</v>
       </c>
       <c r="F37" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C37,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C37,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C37-108,0))))),IF(ROUND($C$9+$C37,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C37,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C37-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C37,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C37,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C37-DaysPerYear,0))))),IF(ROUND($C$9+$C37,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C37,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C37-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G37" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C37,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C37,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C37-108,0))))),IF(ROUND($C$9+$C37,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C37,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C37-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C37,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C37,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C37-DaysPerYear,0))))),IF(ROUND($C$9+$C37,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C37,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C37-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H37" s="50" t="str">
@@ -10344,14 +10375,14 @@
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="38"/>
       <c r="B38" s="39" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C38" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Spelt",CropNames,0))</f>
         <v>16.02</v>
       </c>
       <c r="D38" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C38,0)&gt;108,ROUND($C$9+$C38-108,0),ROUND($C$9+$C38,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C38,0)&gt;DaysPerYear,ROUND($C$9+$C38-DaysPerYear,0),ROUND($C$9+$C38,0))</f>
         <v>50→66</v>
       </c>
       <c r="E38" s="42" t="n">
@@ -10359,11 +10390,11 @@
         <v>18</v>
       </c>
       <c r="F38" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C38,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C38,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C38-108,0))))),IF(ROUND($C$9+$C38,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C38,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C38-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C38,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C38,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C38-DaysPerYear,0))))),IF(ROUND($C$9+$C38,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C38,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C38-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G38" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C38,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C38,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C38-108,0))))),IF(ROUND($C$9+$C38,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C38,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C38-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C38,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C38,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C38-DaysPerYear,0))))),IF(ROUND($C$9+$C38,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C38,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C38-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H38" s="43" t="str">
@@ -10395,14 +10426,14 @@
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="45"/>
       <c r="B39" s="46" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C39" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Flax",CropNames,0))</f>
         <v>16.02</v>
       </c>
       <c r="D39" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C39,0)&gt;108,ROUND($C$9+$C39-108,0),ROUND($C$9+$C39,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C39,0)&gt;DaysPerYear,ROUND($C$9+$C39-DaysPerYear,0),ROUND($C$9+$C39,0))</f>
         <v>50→66</v>
       </c>
       <c r="E39" s="49" t="n">
@@ -10410,11 +10441,11 @@
         <v>18</v>
       </c>
       <c r="F39" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C39,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C39,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C39-108,0))))),IF(ROUND($C$9+$C39,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C39,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C39-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C39,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C39,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C39-DaysPerYear,0))))),IF(ROUND($C$9+$C39,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C39,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C39-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G39" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C39,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C39,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C39-108,0))))),IF(ROUND($C$9+$C39,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C39,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C39-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C39,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C39,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C39-DaysPerYear,0))))),IF(ROUND($C$9+$C39,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C39,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C39-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H39" s="50" t="str">
@@ -10446,14 +10477,14 @@
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="38"/>
       <c r="B40" s="39" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C40" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Sunflower",CropNames,0))</f>
         <v>15.3</v>
       </c>
       <c r="D40" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C40,0)&gt;108,ROUND($C$9+$C40-108,0),ROUND($C$9+$C40,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C40,0)&gt;DaysPerYear,ROUND($C$9+$C40-DaysPerYear,0),ROUND($C$9+$C40,0))</f>
         <v>50→65</v>
       </c>
       <c r="E40" s="42" t="n">
@@ -10461,11 +10492,11 @@
         <v>19</v>
       </c>
       <c r="F40" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C40,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C40,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C40-108,0))))),IF(ROUND($C$9+$C40,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C40,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C40-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C40,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C40,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C40-DaysPerYear,0))))),IF(ROUND($C$9+$C40,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C40,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C40-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G40" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C40,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C40,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C40-108,0))))),IF(ROUND($C$9+$C40,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C40,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C40-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C40,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C40,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C40-DaysPerYear,0))))),IF(ROUND($C$9+$C40,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C40,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C40-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H40" s="43" t="str">
@@ -10497,14 +10528,14 @@
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="45"/>
       <c r="B41" s="46" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C41" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Soybean",CropNames,0))</f>
         <v>10.26</v>
       </c>
       <c r="D41" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C41,0)&gt;108,ROUND($C$9+$C41-108,0),ROUND($C$9+$C41,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C41,0)&gt;DaysPerYear,ROUND($C$9+$C41-DaysPerYear,0),ROUND($C$9+$C41,0))</f>
         <v>50→60</v>
       </c>
       <c r="E41" s="49" t="n">
@@ -10512,11 +10543,11 @@
         <v>24</v>
       </c>
       <c r="F41" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C41,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C41,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C41-108,0))))),IF(ROUND($C$9+$C41,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C41,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C41-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C41,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C41,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C41-DaysPerYear,0))))),IF(ROUND($C$9+$C41,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C41,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C41-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G41" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C41,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C41,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C41-108,0))))),IF(ROUND($C$9+$C41,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C41,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C41-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C41,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C41,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C41-DaysPerYear,0))))),IF(ROUND($C$9+$C41,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C41,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C41-DaysPerYear,0))))))</f>
         <v>24.07</v>
       </c>
       <c r="H41" s="50" t="str">
@@ -10548,14 +10579,14 @@
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="38"/>
       <c r="B42" s="39" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C42" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Pumpkin",CropNames,0))</f>
         <v>15.3</v>
       </c>
       <c r="D42" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C42,0)&gt;108,ROUND($C$9+$C42-108,0),ROUND($C$9+$C42,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C42,0)&gt;DaysPerYear,ROUND($C$9+$C42-DaysPerYear,0),ROUND($C$9+$C42,0))</f>
         <v>50→65</v>
       </c>
       <c r="E42" s="42" t="n">
@@ -10563,11 +10594,11 @@
         <v>19</v>
       </c>
       <c r="F42" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C42,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C42,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C42-108,0))))),IF(ROUND($C$9+$C42,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C42,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C42-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C42,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C42,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C42-DaysPerYear,0))))),IF(ROUND($C$9+$C42,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C42,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C42-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G42" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C42,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C42,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C42-108,0))))),IF(ROUND($C$9+$C42,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C42,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C42-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C42,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C42,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C42-DaysPerYear,0))))),IF(ROUND($C$9+$C42,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C42,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C42-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H42" s="43" t="str">
@@ -10599,14 +10630,14 @@
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="45"/>
       <c r="B43" s="46" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C43" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Amaranth",CropNames,0))</f>
         <v>16.02</v>
       </c>
       <c r="D43" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C43,0)&gt;108,ROUND($C$9+$C43-108,0),ROUND($C$9+$C43,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C43,0)&gt;DaysPerYear,ROUND($C$9+$C43-DaysPerYear,0),ROUND($C$9+$C43,0))</f>
         <v>50→66</v>
       </c>
       <c r="E43" s="49" t="n">
@@ -10614,11 +10645,11 @@
         <v>18</v>
       </c>
       <c r="F43" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C43,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C43,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C43-108,0))))),IF(ROUND($C$9+$C43,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C43,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C43-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C43,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C43,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C43-DaysPerYear,0))))),IF(ROUND($C$9+$C43,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C43,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C43-DaysPerYear,0))))))</f>
         <v>4.66</v>
       </c>
       <c r="G43" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C43,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C43,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C43-108,0))))),IF(ROUND($C$9+$C43,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C43,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C43-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C43,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C43,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C43-DaysPerYear,0))))),IF(ROUND($C$9+$C43,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C43,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C43-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H43" s="50" t="str">
@@ -10650,14 +10681,14 @@
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="38"/>
       <c r="B44" s="39" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C44" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Cassava",CropNames,0))</f>
         <v>39.6</v>
       </c>
       <c r="D44" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C44,0)&gt;108,ROUND($C$9+$C44-108,0),ROUND($C$9+$C44,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C44,0)&gt;DaysPerYear,ROUND($C$9+$C44-DaysPerYear,0),ROUND($C$9+$C44,0))</f>
         <v>50→90</v>
       </c>
       <c r="E44" s="42" t="n">
@@ -10665,11 +10696,11 @@
         <v>0</v>
       </c>
       <c r="F44" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C44,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C44,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C44-108,0))))),IF(ROUND($C$9+$C44,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C44,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C44-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C44,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C44,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C44-DaysPerYear,0))))),IF(ROUND($C$9+$C44,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C44,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C44-DaysPerYear,0))))))</f>
         <v>-16.52</v>
       </c>
       <c r="G44" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C44,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C44,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C44-108,0))))),IF(ROUND($C$9+$C44,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C44,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C44-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C44,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C44,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C44-DaysPerYear,0))))),IF(ROUND($C$9+$C44,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C44,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C44-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H44" s="43" t="str">
@@ -10701,14 +10732,14 @@
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="45"/>
       <c r="B45" s="46" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C45" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Peanut",CropNames,0))</f>
         <v>19.8</v>
       </c>
       <c r="D45" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C45,0)&gt;108,ROUND($C$9+$C45-108,0),ROUND($C$9+$C45,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C45,0)&gt;DaysPerYear,ROUND($C$9+$C45-DaysPerYear,0),ROUND($C$9+$C45,0))</f>
         <v>50→70</v>
       </c>
       <c r="E45" s="49" t="n">
@@ -10716,11 +10747,11 @@
         <v>14</v>
       </c>
       <c r="F45" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C45,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C45,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C45-108,0))))),IF(ROUND($C$9+$C45,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C45,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C45-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C45,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C45,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C45-DaysPerYear,0))))),IF(ROUND($C$9+$C45,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C45,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C45-DaysPerYear,0))))))</f>
         <v>3.62</v>
       </c>
       <c r="G45" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C45,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C45,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C45-108,0))))),IF(ROUND($C$9+$C45,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C45,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C45-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C45,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C45,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C45-DaysPerYear,0))))),IF(ROUND($C$9+$C45,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C45,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C45-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H45" s="50" t="str">
@@ -10752,14 +10783,14 @@
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="38"/>
       <c r="B46" s="39" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C46" s="40" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Rice",CropNames,0))</f>
         <v>18</v>
       </c>
       <c r="D46" s="41" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C46,0)&gt;108,ROUND($C$9+$C46-108,0),ROUND($C$9+$C46,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C46,0)&gt;DaysPerYear,ROUND($C$9+$C46-DaysPerYear,0),ROUND($C$9+$C46,0))</f>
         <v>50→68</v>
       </c>
       <c r="E46" s="42" t="n">
@@ -10767,11 +10798,11 @@
         <v>16</v>
       </c>
       <c r="F46" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C46,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C46,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C46-108,0))))),IF(ROUND($C$9+$C46,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C46,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C46-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C46,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C46,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C46-DaysPerYear,0))))),IF(ROUND($C$9+$C46,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C46,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C46-DaysPerYear,0))))))</f>
         <v>3.79</v>
       </c>
       <c r="G46" s="40" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C46,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C46,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C46-108,0))))),IF(ROUND($C$9+$C46,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C46,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C46-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C46,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C46,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C46-DaysPerYear,0))))),IF(ROUND($C$9+$C46,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C46,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C46-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H46" s="43" t="str">
@@ -10803,14 +10834,14 @@
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="45"/>
       <c r="B47" s="46" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C47" s="47" t="n">
         <f aca="false">INDEX(Crops!$F$5:$F$22,MATCH("Pineapple",CropNames,0))</f>
         <v>50.4</v>
       </c>
       <c r="D47" s="48" t="str">
-        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C47,0)&gt;108,ROUND($C$9+$C47-108,0),ROUND($C$9+$C47,0))</f>
+        <f aca="false">$C$9&amp;"→"&amp;IF(ROUND($C$9+$C47,0)&gt;DaysPerYear,ROUND($C$9+$C47-DaysPerYear,0),ROUND($C$9+$C47,0))</f>
         <v>50→100</v>
       </c>
       <c r="E47" s="49" t="n">
@@ -10818,11 +10849,11 @@
         <v>0</v>
       </c>
       <c r="F47" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C47,0)&lt;=108,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C47,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,108)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C47-108,0))))),IF(ROUND($C$9+$C47,0)&lt;=108,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C47,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,108)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C47-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C47,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C47,0))),MIN(MIN(INDEX(Climate!$H$5:$H$112,$C$9):INDEX(Climate!$H$5:$H$112,ClimateRows)),MIN(INDEX(Climate!$H$5:$H$112,1):INDEX(Climate!$H$5:$H$112,ROUND($C$9+$C47-DaysPerYear,0))))),IF(ROUND($C$9+$C47,0)&lt;=DaysPerYear,MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C47,0))),MIN(MIN(INDEX(Climate!$E$5:$E$112,$C$9):INDEX(Climate!$E$5:$E$112,ClimateRows)),MIN(INDEX(Climate!$E$5:$E$112,1):INDEX(Climate!$E$5:$E$112,ROUND($C$9+$C47-DaysPerYear,0))))))</f>
         <v>-26.55</v>
       </c>
       <c r="G47" s="47" t="n">
-        <f aca="false">IF($C$11,IF(ROUND($C$9+$C47,0)&lt;=108,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C47,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,108)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C47-108,0))))),IF(ROUND($C$9+$C47,0)&lt;=108,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C47,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,108)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C47-108,0))))))</f>
+        <f aca="false">IF($C$11,IF(ROUND($C$9+$C47,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C47,0))),MAX(MAX(INDEX(Climate!$I$5:$I$112,$C$9):INDEX(Climate!$I$5:$I$112,ClimateRows)),MAX(INDEX(Climate!$I$5:$I$112,1):INDEX(Climate!$I$5:$I$112,ROUND($C$9+$C47-DaysPerYear,0))))),IF(ROUND($C$9+$C47,0)&lt;=DaysPerYear,MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C47,0))),MAX(MAX(INDEX(Climate!$F$5:$F$112,$C$9):INDEX(Climate!$F$5:$F$112,ClimateRows)),MAX(INDEX(Climate!$F$5:$F$112,1):INDEX(Climate!$F$5:$F$112,ROUND($C$9+$C47-DaysPerYear,0))))))</f>
         <v>24.64</v>
       </c>
       <c r="H47" s="50" t="str">
@@ -10853,7 +10884,7 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K48" s="52" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L48" s="53" t="n">
         <f aca="false">LARGE($L$30:$L$47,3)</f>
@@ -10862,7 +10893,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="K49" s="52" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="L49" s="53" t="n">
         <f aca="false">LARGE($L$30:$L$47,10)</f>
@@ -10872,7 +10903,7 @@
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="21"/>
       <c r="B51" s="5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
@@ -10889,37 +10920,37 @@
     </row>
     <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="37" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D53" s="37" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G53" s="37" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I53" s="37" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J53" s="37" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="38"/>
       <c r="B54" s="43" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C54" s="43" t="str">
         <f aca="false">INDEX($B$30:$B$47,MATCH(LARGE($L$30:$L$47,1),$L$30:$L$47,0))</f>
@@ -10961,7 +10992,7 @@
     <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="45"/>
       <c r="B55" s="50" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C55" s="50" t="str">
         <f aca="false">INDEX($B$30:$B$47,MATCH(LARGE($L$30:$L$47,2),$L$30:$L$47,0))</f>
@@ -11003,7 +11034,7 @@
     <row r="56" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="38"/>
       <c r="B56" s="43" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C56" s="43" t="str">
         <f aca="false">INDEX($B$30:$B$47,MATCH(LARGE($L$30:$L$47,3),$L$30:$L$47,0))</f>
@@ -11045,7 +11076,7 @@
     <row r="58" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="21"/>
       <c r="B58" s="5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C58" s="5"/>
       <c r="D58" s="5"/>
@@ -11186,7 +11217,7 @@
     <row r="68" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="21"/>
       <c r="B68" s="5" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C68" s="5"/>
       <c r="D68" s="5"/>
@@ -11222,7 +11253,7 @@
     <row r="70" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="21"/>
       <c r="B70" s="5" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C70" s="5"/>
       <c r="D70" s="5"/>
@@ -11239,7 +11270,7 @@
     </row>
     <row r="72" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B72" s="30" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C72" s="30"/>
       <c r="D72" s="30"/>
@@ -11256,7 +11287,7 @@
     </row>
     <row r="73" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B73" s="30" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C73" s="30"/>
       <c r="D73" s="30"/>
@@ -11273,7 +11304,7 @@
     </row>
     <row r="74" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B74" s="19" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C74" s="19"/>
       <c r="D74" s="19"/>
@@ -11290,7 +11321,7 @@
     </row>
     <row r="75" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B75" s="19" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C75" s="19"/>
       <c r="D75" s="19"/>
@@ -11307,7 +11338,7 @@
     </row>
     <row r="76" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B76" s="19" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C76" s="19"/>
       <c r="D76" s="19"/>
@@ -11324,7 +11355,7 @@
     </row>
     <row r="77" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B77" s="19" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
@@ -11356,7 +11387,7 @@
     </row>
     <row r="79" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B79" s="19" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C79" s="19"/>
       <c r="D79" s="19"/>
@@ -11388,7 +11419,7 @@
     </row>
     <row r="81" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B81" s="19" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C81" s="19"/>
       <c r="D81" s="19"/>
@@ -11405,7 +11436,7 @@
     </row>
     <row r="82" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B82" s="19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C82" s="19"/>
       <c r="D82" s="19"/>
@@ -11422,7 +11453,7 @@
     </row>
     <row r="83" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B83" s="19" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C83" s="19"/>
       <c r="D83" s="19"/>
@@ -11439,7 +11470,7 @@
     </row>
     <row r="84" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B84" s="19" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C84" s="19"/>
       <c r="D84" s="19"/>
@@ -11456,7 +11487,7 @@
     </row>
     <row r="85" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B85" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C85" s="19"/>
       <c r="D85" s="19"/>
@@ -11473,7 +11504,7 @@
     </row>
     <row r="86" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B86" s="19" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C86" s="19"/>
       <c r="D86" s="19"/>
@@ -11491,7 +11522,7 @@
     <row r="88" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="21"/>
       <c r="B88" s="5" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C88" s="5"/>
       <c r="D88" s="5"/>
@@ -11673,7 +11704,7 @@
     <row r="1" customFormat="false" ht="3.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="58" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B2" s="58"/>
       <c r="C2" s="58"/>
@@ -11691,7 +11722,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="59" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B3" s="59"/>
       <c r="C3" s="59"/>
@@ -11710,7 +11741,7 @@
     <row r="4" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -11729,19 +11760,19 @@
     <row r="6" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="60" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C7" s="60"/>
       <c r="D7" s="60"/>
       <c r="E7" s="60"/>
       <c r="F7" s="60" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="G7" s="60"/>
       <c r="H7" s="60"/>
       <c r="I7" s="60"/>
       <c r="J7" s="60" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="K7" s="60"/>
       <c r="L7" s="60"/>
@@ -11749,7 +11780,7 @@
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="61" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C8" s="61"/>
       <c r="D8" s="61"/>
@@ -11771,19 +11802,19 @@
     </row>
     <row r="9" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="62" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C9" s="62"/>
       <c r="D9" s="62"/>
       <c r="E9" s="62"/>
       <c r="F9" s="62" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G9" s="62"/>
       <c r="H9" s="62"/>
       <c r="I9" s="62"/>
       <c r="J9" s="62" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K9" s="62"/>
       <c r="L9" s="62"/>
@@ -11792,19 +11823,19 @@
     <row r="10" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="60" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
       <c r="E11" s="60"/>
       <c r="F11" s="60" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G11" s="60"/>
       <c r="H11" s="60"/>
       <c r="I11" s="60"/>
       <c r="J11" s="60" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K11" s="60"/>
       <c r="L11" s="60"/>
@@ -11812,14 +11843,14 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="61" t="str">
-        <f aca="false">COUNTIF(Climate!$D$5:$D$112,"&gt;0")&amp;" of 108"</f>
+        <f aca="false">COUNTIF(Climate!$D$5:$D$112,"&gt;0")&amp;" of "&amp;DaysPerYear</f>
         <v>50 of 108</v>
       </c>
       <c r="C12" s="61"/>
       <c r="D12" s="61"/>
       <c r="E12" s="61"/>
       <c r="F12" s="61" t="str">
-        <f aca="false">COUNTIF(Climate!$E$5:$E$112,"&lt;0")&amp;" of 108"</f>
+        <f aca="false">COUNTIF(Climate!$E$5:$E$112,"&lt;0")&amp;" of "&amp;DaysPerYear</f>
         <v>75 of 108</v>
       </c>
       <c r="G12" s="61"/>
@@ -11835,19 +11866,19 @@
     </row>
     <row r="13" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="62" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C13" s="62"/>
       <c r="D13" s="62"/>
       <c r="E13" s="62"/>
       <c r="F13" s="62" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G13" s="62"/>
       <c r="H13" s="62"/>
       <c r="I13" s="62"/>
       <c r="J13" s="62" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K13" s="62"/>
       <c r="L13" s="62"/>
@@ -11856,7 +11887,7 @@
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -11906,7 +11937,7 @@
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -11925,7 +11956,7 @@
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="63"/>
       <c r="B49" s="64" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C49" s="64"/>
       <c r="D49" s="64"/>
@@ -11946,7 +11977,7 @@
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="66"/>
       <c r="B50" s="67" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C50" s="67"/>
       <c r="D50" s="67"/>
@@ -11967,7 +11998,7 @@
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="63"/>
       <c r="B51" s="64" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C51" s="64"/>
       <c r="D51" s="64"/>
@@ -11988,7 +12019,7 @@
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="66"/>
       <c r="B52" s="67" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C52" s="67"/>
       <c r="D52" s="67"/>
@@ -12009,7 +12040,7 @@
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="63"/>
       <c r="B53" s="64" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C53" s="64"/>
       <c r="D53" s="64"/>
@@ -12030,7 +12061,7 @@
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B55" s="5"/>
       <c r="C55" s="5"/>
@@ -12054,7 +12085,7 @@
       <c r="C56" s="69"/>
       <c r="D56" s="69"/>
       <c r="E56" s="70" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="F56" s="70"/>
       <c r="G56" s="70"/>
@@ -12074,7 +12105,7 @@
       <c r="C57" s="71"/>
       <c r="D57" s="71"/>
       <c r="E57" s="72" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F57" s="72"/>
       <c r="G57" s="72"/>
@@ -12094,7 +12125,7 @@
       <c r="C58" s="69"/>
       <c r="D58" s="69"/>
       <c r="E58" s="70" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F58" s="70"/>
       <c r="G58" s="70"/>
@@ -12114,7 +12145,7 @@
       <c r="C59" s="71"/>
       <c r="D59" s="71"/>
       <c r="E59" s="72" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F59" s="72"/>
       <c r="G59" s="72"/>
@@ -12134,7 +12165,7 @@
       <c r="C60" s="69"/>
       <c r="D60" s="69"/>
       <c r="E60" s="70" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F60" s="70"/>
       <c r="G60" s="70"/>
@@ -12154,7 +12185,7 @@
       <c r="C61" s="71"/>
       <c r="D61" s="71"/>
       <c r="E61" s="72" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F61" s="72"/>
       <c r="G61" s="72"/>
@@ -12233,7 +12264,7 @@
     <tabColor rgb="FF52B788"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
@@ -12245,7 +12276,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12254,7 +12285,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -12270,16 +12301,16 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="37" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12294,78 +12325,78 @@
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="38"/>
       <c r="B6" s="73" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C6" s="74" t="n">
         <v>9</v>
       </c>
       <c r="D6" s="75" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E6" s="76" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="45"/>
       <c r="B7" s="77" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C7" s="74" t="n">
         <v>12</v>
       </c>
       <c r="D7" s="78"/>
       <c r="E7" s="79" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="38"/>
       <c r="B8" s="73" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C8" s="74" t="n">
         <v>24</v>
       </c>
       <c r="D8" s="75" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E8" s="76" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="45"/>
       <c r="B9" s="77" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C9" s="80" t="n">
         <f aca="false">DaysPerMonth*MonthsPerYear</f>
         <v>108</v>
       </c>
       <c r="D9" s="78" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E9" s="79" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="38"/>
       <c r="B10" s="73" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C10" s="74" t="n">
         <v>5</v>
       </c>
       <c r="D10" s="75"/>
       <c r="E10" s="76" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -12375,37 +12406,37 @@
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="45"/>
       <c r="B12" s="77" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C12" s="81" t="n">
         <v>3.5</v>
       </c>
       <c r="D12" s="78" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E12" s="79" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="38"/>
       <c r="B13" s="73" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C13" s="82" t="n">
         <f aca="false">HoursPerDay/TickMean</f>
         <v>6.85714285714286</v>
       </c>
       <c r="D13" s="75" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E13" s="76" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -12415,81 +12446,81 @@
     <row r="15" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="45"/>
       <c r="B15" s="77" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="C15" s="81" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="78" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E15" s="79" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="38"/>
       <c r="B16" s="73" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C16" s="74" t="n">
         <v>19</v>
       </c>
       <c r="D16" s="75" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E16" s="76" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="45"/>
       <c r="B17" s="77" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C17" s="81" t="n">
         <v>0.1</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="E17" s="79" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="38"/>
       <c r="B18" s="73" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C18" s="74" t="n">
         <v>10</v>
       </c>
       <c r="D18" s="75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E18" s="76" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="45"/>
       <c r="B19" s="77" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="C19" s="81" t="n">
         <v>0.1</v>
       </c>
       <c r="D19" s="78" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="E19" s="79" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5"/>
@@ -12499,75 +12530,75 @@
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38"/>
       <c r="B21" s="73" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C21" s="81" t="n">
         <v>0.25</v>
       </c>
       <c r="D21" s="75" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E21" s="76" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="45"/>
       <c r="B22" s="77" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C22" s="74" t="n">
         <v>3</v>
       </c>
       <c r="D22" s="78"/>
       <c r="E22" s="79" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="38"/>
       <c r="B23" s="73" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C23" s="74" t="n">
         <v>150</v>
       </c>
       <c r="D23" s="75"/>
       <c r="E23" s="76" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="45"/>
       <c r="B24" s="77" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C24" s="74" t="n">
         <v>100</v>
       </c>
       <c r="D24" s="78"/>
       <c r="E24" s="79" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="38"/>
       <c r="B25" s="73" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C25" s="81" t="n">
         <v>0.05</v>
       </c>
       <c r="D25" s="75" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E25" s="76" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
@@ -12577,90 +12608,90 @@
     <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="45"/>
       <c r="B27" s="77" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C27" s="74" t="n">
         <v>48</v>
       </c>
       <c r="D27" s="78" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E27" s="79" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="38"/>
       <c r="B28" s="73" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C28" s="81" t="n">
         <v>0.1</v>
       </c>
       <c r="D28" s="75"/>
       <c r="E28" s="76" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="45"/>
       <c r="B29" s="77" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C29" s="74" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="78" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E29" s="79" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="38"/>
       <c r="B30" s="73" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C30" s="74" t="n">
         <v>9999</v>
       </c>
       <c r="D30" s="75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E30" s="76" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="45"/>
       <c r="B31" s="77" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C31" s="81" t="n">
         <v>0.5</v>
       </c>
       <c r="D31" s="78"/>
       <c r="E31" s="79" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="38"/>
       <c r="B32" s="73" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C32" s="81" t="n">
         <v>0.5</v>
       </c>
       <c r="D32" s="75"/>
       <c r="E32" s="76" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5"/>
@@ -12670,36 +12701,36 @@
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="45"/>
       <c r="B34" s="77" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="C34" s="74" t="n">
         <v>96</v>
       </c>
       <c r="D34" s="78" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E34" s="79" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="38"/>
       <c r="B35" s="73" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C35" s="81" t="n">
         <v>0.75</v>
       </c>
       <c r="D35" s="75" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E35" s="76" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -12709,70 +12740,70 @@
     <row r="37" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="45"/>
       <c r="B37" s="77" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="C37" s="83" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D37" s="78" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E37" s="79" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="38"/>
       <c r="B38" s="73" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C38" s="83" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D38" s="75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E38" s="76" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="45"/>
       <c r="B39" s="77" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C39" s="83" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="D39" s="78" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E39" s="79" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="38"/>
       <c r="B40" s="73" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C40" s="83" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D40" s="75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E40" s="76" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -12782,37 +12813,37 @@
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="45"/>
       <c r="B42" s="77" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C42" s="74" t="n">
         <v>5</v>
       </c>
       <c r="D42" s="78" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E42" s="79" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="38"/>
       <c r="B43" s="73" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C43" s="83" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="D43" s="75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E43" s="76" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -12822,37 +12853,37 @@
     <row r="45" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="45"/>
       <c r="B45" s="77" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C45" s="83" t="b">
         <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="D45" s="84" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="E45" s="79" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="38"/>
       <c r="B46" s="73" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C46" s="81" t="n">
         <v>0.25</v>
       </c>
       <c r="D46" s="85" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="E46" s="76" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -12862,96 +12893,96 @@
     <row r="48" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="45"/>
       <c r="B48" s="77" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C48" s="81" t="n">
         <v>0.557</v>
       </c>
       <c r="D48" s="78" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E48" s="79" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="38"/>
       <c r="B49" s="73" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C49" s="74" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D49" s="75" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E49" s="76" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="45"/>
       <c r="B50" s="77" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C50" s="74" t="n">
         <v>0</v>
       </c>
       <c r="D50" s="78" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E50" s="79" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="38"/>
       <c r="B51" s="73" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="C51" s="81" t="n">
         <v>-2.13</v>
       </c>
       <c r="D51" s="75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E51" s="76" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="45"/>
       <c r="B52" s="77" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C52" s="81" t="n">
         <v>36.5</v>
       </c>
       <c r="D52" s="78" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E52" s="79" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="38"/>
       <c r="B53" s="73" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C53" s="81" t="n">
         <v>17.97</v>
       </c>
       <c r="D53" s="75" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="E53" s="76" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
@@ -12961,29 +12992,43 @@
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="45"/>
       <c r="B55" s="77" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C55" s="74" t="n">
         <v>50</v>
       </c>
       <c r="D55" s="78" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E55" s="79" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="38"/>
       <c r="B56" s="73" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="C56" s="74" t="n">
         <v>1386</v>
       </c>
       <c r="D56" s="75"/>
       <c r="E56" s="76" t="s">
-        <v>289</v>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -13033,7 +13078,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -13048,7 +13093,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -13061,7 +13106,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="52" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M2" s="86" t="n">
         <f aca="false">MATCH(1,J65:J112,0)+60</f>
@@ -13083,37 +13128,37 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17776,7 +17821,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -17798,7 +17843,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -17840,69 +17885,69 @@
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C4" s="37" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="G4" s="37" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="I4" s="37" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K4" s="37" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="L4" s="37" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="M4" s="37" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="N4" s="37" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="O4" s="37" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="R4" s="37" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="93" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B5" s="94" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C5" s="94" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D5" s="95" t="n">
         <v>9</v>
@@ -17915,7 +17960,7 @@
         <v>16.02</v>
       </c>
       <c r="G5" s="98" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H5" s="99" t="n">
         <v>35</v>
@@ -17945,24 +17990,24 @@
         <v>0.75</v>
       </c>
       <c r="P5" s="98" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="Q5" s="99" t="n">
         <v>0.7</v>
       </c>
       <c r="R5" s="76" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="102" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B6" s="103" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C6" s="103" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D6" s="104" t="n">
         <v>7</v>
@@ -17975,7 +18020,7 @@
         <v>9.27</v>
       </c>
       <c r="G6" s="107" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H6" s="108" t="n">
         <v>34.3</v>
@@ -18005,24 +18050,24 @@
         <v>0.75</v>
       </c>
       <c r="P6" s="107" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q6" s="108" t="n">
         <v>3</v>
       </c>
       <c r="R6" s="79" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="93" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="94" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="94" t="s">
         <v>330</v>
-      </c>
-      <c r="B7" s="94" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="94" t="s">
-        <v>324</v>
       </c>
       <c r="D7" s="95" t="n">
         <v>8</v>
@@ -18035,7 +18080,7 @@
         <v>15.75</v>
       </c>
       <c r="G7" s="98" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H7" s="99" t="n">
         <v>17.5</v>
@@ -18065,24 +18110,24 @@
         <v>0.75</v>
       </c>
       <c r="P7" s="98" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="Q7" s="99" t="n">
         <v>4</v>
       </c>
       <c r="R7" s="76" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="102" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B8" s="103" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C8" s="103" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D8" s="104" t="n">
         <v>9</v>
@@ -18095,7 +18140,7 @@
         <v>24.03</v>
       </c>
       <c r="G8" s="107" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H8" s="108" t="n">
         <v>35</v>
@@ -18125,24 +18170,24 @@
         <v>0.75</v>
       </c>
       <c r="P8" s="107" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q8" s="108" t="n">
         <v>3</v>
       </c>
       <c r="R8" s="79" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="93" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B9" s="94" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D9" s="95" t="n">
         <v>9</v>
@@ -18155,7 +18200,7 @@
         <v>24.03</v>
       </c>
       <c r="G9" s="98" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H9" s="99" t="n">
         <v>35</v>
@@ -18185,24 +18230,24 @@
         <v>0.75</v>
       </c>
       <c r="P9" s="98" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="Q9" s="99" t="n">
         <v>3</v>
       </c>
       <c r="R9" s="76" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="102" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B10" s="103" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C10" s="103" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D10" s="104" t="n">
         <v>7</v>
@@ -18215,7 +18260,7 @@
         <v>13.86</v>
       </c>
       <c r="G10" s="107" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H10" s="108" t="n">
         <v>30</v>
@@ -18239,24 +18284,24 @@
       <c r="N10" s="112"/>
       <c r="O10" s="112"/>
       <c r="P10" s="107" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="Q10" s="108" t="n">
         <v>3</v>
       </c>
       <c r="R10" s="79" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="93" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B11" s="94" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C11" s="94" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D11" s="95" t="n">
         <v>5</v>
@@ -18269,7 +18314,7 @@
         <v>7.2</v>
       </c>
       <c r="G11" s="98" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H11" s="99" t="n">
         <v>24</v>
@@ -18293,24 +18338,24 @@
       <c r="N11" s="116"/>
       <c r="O11" s="116"/>
       <c r="P11" s="98" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="Q11" s="99" t="n">
         <v>3</v>
       </c>
       <c r="R11" s="76" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="102" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B12" s="103" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C12" s="103" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D12" s="104" t="n">
         <v>12</v>
@@ -18323,7 +18368,7 @@
         <v>12.375</v>
       </c>
       <c r="G12" s="107" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H12" s="108" t="n">
         <v>36.67</v>
@@ -18347,24 +18392,24 @@
       <c r="N12" s="112"/>
       <c r="O12" s="112"/>
       <c r="P12" s="107" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="Q12" s="108" t="n">
         <v>0.85</v>
       </c>
       <c r="R12" s="79" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="93" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B13" s="94" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="C13" s="94" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D13" s="95" t="n">
         <v>9</v>
@@ -18377,7 +18422,7 @@
         <v>16.02</v>
       </c>
       <c r="G13" s="98" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H13" s="99" t="n">
         <v>35</v>
@@ -18399,24 +18444,24 @@
       <c r="N13" s="116"/>
       <c r="O13" s="116"/>
       <c r="P13" s="98" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Q13" s="99" t="n">
         <v>0.7</v>
       </c>
       <c r="R13" s="76" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="102" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B14" s="103" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C14" s="103" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="D14" s="104" t="n">
         <v>9</v>
@@ -18429,7 +18474,7 @@
         <v>16.02</v>
       </c>
       <c r="G14" s="107" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H14" s="108" t="n">
         <v>44.4</v>
@@ -18451,24 +18496,24 @@
       <c r="N14" s="112"/>
       <c r="O14" s="112"/>
       <c r="P14" s="107" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="Q14" s="108" t="n">
         <v>0.7</v>
       </c>
       <c r="R14" s="79" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="93" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B15" s="94" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C15" s="94" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D15" s="95" t="n">
         <v>12</v>
@@ -18481,7 +18526,7 @@
         <v>15.3</v>
       </c>
       <c r="G15" s="98" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H15" s="99" t="n">
         <v>36</v>
@@ -18503,24 +18548,24 @@
       <c r="N15" s="116"/>
       <c r="O15" s="116"/>
       <c r="P15" s="98" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="Q15" s="99" t="n">
         <v>0.7</v>
       </c>
       <c r="R15" s="76" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="102" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B16" s="103" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C16" s="103" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D16" s="104" t="n">
         <v>11</v>
@@ -18533,7 +18578,7 @@
         <v>10.26</v>
       </c>
       <c r="G16" s="107" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H16" s="108" t="n">
         <v>32</v>
@@ -18555,24 +18600,24 @@
       <c r="N16" s="112"/>
       <c r="O16" s="112"/>
       <c r="P16" s="107" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="Q16" s="108" t="n">
         <v>2</v>
       </c>
       <c r="R16" s="79" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="93" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B17" s="94" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C17" s="94" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="D17" s="95" t="n">
         <v>8</v>
@@ -18585,7 +18630,7 @@
         <v>15.3</v>
       </c>
       <c r="G17" s="98" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H17" s="99" t="n">
         <v>30</v>
@@ -18607,24 +18652,24 @@
       <c r="N17" s="116"/>
       <c r="O17" s="116"/>
       <c r="P17" s="98" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="Q17" s="99" t="n">
         <v>0.7</v>
       </c>
       <c r="R17" s="76" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="102" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B18" s="103" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C18" s="103" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D18" s="104" t="n">
         <v>9</v>
@@ -18637,7 +18682,7 @@
         <v>16.02</v>
       </c>
       <c r="G18" s="107" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H18" s="108" t="n">
         <v>13.33</v>
@@ -18663,24 +18708,24 @@
       <c r="N18" s="112"/>
       <c r="O18" s="112"/>
       <c r="P18" s="107" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="Q18" s="108" t="n">
         <v>2</v>
       </c>
       <c r="R18" s="79" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="93" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B19" s="94" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C19" s="94" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D19" s="95" t="n">
         <v>9</v>
@@ -18693,7 +18738,7 @@
         <v>39.6</v>
       </c>
       <c r="G19" s="98" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H19" s="99" t="n">
         <v>22.2</v>
@@ -18719,24 +18764,24 @@
       <c r="N19" s="116"/>
       <c r="O19" s="116"/>
       <c r="P19" s="98" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="Q19" s="99" t="n">
         <v>5</v>
       </c>
       <c r="R19" s="76" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="102" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B20" s="103" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C20" s="103" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D20" s="104" t="n">
         <v>9</v>
@@ -18749,7 +18794,7 @@
         <v>19.8</v>
       </c>
       <c r="G20" s="107" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H20" s="108" t="n">
         <v>40</v>
@@ -18775,7 +18820,7 @@
       <c r="N20" s="112"/>
       <c r="O20" s="112"/>
       <c r="P20" s="107" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="Q20" s="108" t="n">
         <v>4</v>
@@ -18784,13 +18829,13 @@
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="93" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B21" s="94" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C21" s="94" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D21" s="95" t="n">
         <v>10</v>
@@ -18803,7 +18848,7 @@
         <v>18</v>
       </c>
       <c r="G21" s="98" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H21" s="99" t="n">
         <v>45</v>
@@ -18829,7 +18874,7 @@
       <c r="N21" s="116"/>
       <c r="O21" s="116"/>
       <c r="P21" s="98" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="Q21" s="99" t="n">
         <v>0.7</v>
@@ -18838,13 +18883,13 @@
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="102" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="B22" s="103" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="103" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="D22" s="104" t="n">
         <v>16</v>
@@ -18857,7 +18902,7 @@
         <v>50.4</v>
       </c>
       <c r="G22" s="107" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H22" s="108" t="n">
         <v>14</v>
@@ -18883,18 +18928,18 @@
       <c r="N22" s="112"/>
       <c r="O22" s="112"/>
       <c r="P22" s="107" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="Q22" s="108" t="n">
         <v>0.7</v>
       </c>
       <c r="R22" s="79" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -18950,7 +18995,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -18960,7 +19005,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -18979,132 +19024,132 @@
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="37"/>
       <c r="B4" s="37" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="D4" s="37" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="E4" s="37" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F4" s="37" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="38"/>
       <c r="B5" s="98" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C5" s="117" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="D5" s="95" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="76" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="45"/>
       <c r="B6" s="107" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C6" s="118" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D6" s="104" t="n">
         <v>25</v>
       </c>
       <c r="E6" s="79" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="F6" s="79" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="38"/>
       <c r="B7" s="98" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C7" s="117" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D7" s="95" t="n">
         <v>50</v>
       </c>
       <c r="E7" s="76" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="F7" s="76" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="45"/>
       <c r="B8" s="107" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C8" s="118" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D8" s="104" t="n">
         <v>65</v>
       </c>
       <c r="E8" s="79" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F8" s="79" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="38"/>
       <c r="B9" s="98" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C9" s="117" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D9" s="95" t="n">
         <v>80</v>
       </c>
       <c r="E9" s="76" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="F9" s="76" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="45"/>
       <c r="B10" s="119" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C10" s="120" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="D10" s="121" t="n">
         <v>30</v>
       </c>
       <c r="E10" s="122" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F10" s="123" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -19114,7 +19159,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="6" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
@@ -19123,7 +19168,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="6" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
@@ -19132,7 +19177,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="6" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C15" s="6"/>
       <c r="D15" s="6"/>
@@ -19141,7 +19186,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="6" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="6"/>
@@ -19150,7 +19195,7 @@
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -19199,7 +19244,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19213,7 +19258,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="20"/>
@@ -19239,7 +19284,7 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -19254,28 +19299,28 @@
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="37"/>
       <c r="B5" s="37" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D5" s="37" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E5" s="37" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="38"/>
       <c r="B6" s="125" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C6" s="95" t="n">
         <v>0</v>
@@ -19287,16 +19332,16 @@
         <v>60</v>
       </c>
       <c r="F6" s="98" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G6" s="76" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="45"/>
       <c r="B7" s="126" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C7" s="104" t="n">
         <v>13</v>
@@ -19308,16 +19353,16 @@
         <v>44</v>
       </c>
       <c r="F7" s="78" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G7" s="79" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="38"/>
       <c r="B8" s="125" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C8" s="95" t="n">
         <v>3</v>
@@ -19329,16 +19374,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="75" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G8" s="76" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="45"/>
       <c r="B9" s="126" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C9" s="104" t="n">
         <v>40</v>
@@ -19350,15 +19395,15 @@
         <v>8</v>
       </c>
       <c r="F9" s="78" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G9" s="79" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -19372,7 +19417,7 @@
     </row>
     <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="127" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B13" s="127"/>
       <c r="C13" s="127"/>
@@ -19383,13 +19428,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="128" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C15" s="129" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="I15" s="130" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="J15" s="131" t="n">
         <f aca="false">VLOOKUP($C$15,$B$6:$E$9,2,FALSE())</f>
@@ -19398,7 +19443,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="128" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C16" s="132" t="n">
         <v>50</v>
@@ -19410,10 +19455,10 @@
         <v>50</v>
       </c>
       <c r="F16" s="130" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="I16" s="130" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="J16" s="131" t="n">
         <f aca="false">VLOOKUP($C$15,$B$6:$E$9,3,FALSE())</f>
@@ -19422,7 +19467,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I17" s="130" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="J17" s="131" t="n">
         <f aca="false">VLOOKUP($C$15,$B$6:$E$9,4,FALSE())</f>
@@ -19431,7 +19476,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I18" s="130" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="J18" s="131" t="n">
         <f aca="false">IF($C$15="Potash",0,0)</f>
@@ -19441,25 +19486,25 @@
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="37"/>
       <c r="B19" s="37" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D19" s="37" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E19" s="37" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="I19" s="130" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="J19" s="131" t="n">
         <f aca="false">IF($C$15="Potash",0,0)</f>
@@ -19489,7 +19534,7 @@
       </c>
       <c r="G20" s="38"/>
       <c r="I20" s="130" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="J20" s="131" t="n">
         <f aca="false">IF($C$15="Potash",15,0)</f>
@@ -19514,11 +19559,11 @@
         <v>54</v>
       </c>
       <c r="F21" s="78" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G21" s="45"/>
       <c r="I21" s="130" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="J21" s="131" t="n">
         <f aca="false">INT(ROUND($J$15*PerkPct,1))</f>
@@ -19543,11 +19588,11 @@
         <v>56</v>
       </c>
       <c r="F22" s="75" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G22" s="38"/>
       <c r="I22" s="130" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="J22" s="131" t="n">
         <f aca="false">INT(ROUND($J$16*PerkPct,1))</f>
@@ -19572,11 +19617,11 @@
         <v>58</v>
       </c>
       <c r="F23" s="78" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G23" s="45"/>
       <c r="I23" s="130" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="J23" s="131" t="n">
         <f aca="false">INT(ROUND($J$17*PerkPct,1))</f>
@@ -19601,7 +19646,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="75" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G24" s="38"/>
     </row>
@@ -19623,13 +19668,13 @@
         <v>62</v>
       </c>
       <c r="F25" s="78" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G25" s="45"/>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="127" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="B27" s="127"/>
       <c r="C27" s="127"/>
@@ -19640,7 +19685,7 @@
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="127" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B28" s="127"/>
       <c r="C28" s="127"/>
@@ -19651,7 +19696,7 @@
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -19723,7 +19768,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -19773,7 +19818,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -19823,7 +19868,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="128" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="B3" s="134" t="str">
         <f aca="false">IF(GlobalGH,"ON (+5°C)","OFF")</f>
@@ -19836,10 +19881,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="135" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B4" s="136" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C4" s="136"/>
       <c r="D4" s="136"/>
@@ -19850,7 +19895,7 @@
       <c r="I4" s="136"/>
       <c r="J4" s="136"/>
       <c r="K4" s="136" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="L4" s="136"/>
       <c r="M4" s="136"/>
@@ -19861,7 +19906,7 @@
       <c r="R4" s="136"/>
       <c r="S4" s="136"/>
       <c r="T4" s="136" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="U4" s="136"/>
       <c r="V4" s="136"/>
@@ -19872,7 +19917,7 @@
       <c r="AA4" s="136"/>
       <c r="AB4" s="136"/>
       <c r="AC4" s="136" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="AD4" s="136"/>
       <c r="AE4" s="136"/>
@@ -19883,7 +19928,7 @@
       <c r="AJ4" s="136"/>
       <c r="AK4" s="136"/>
       <c r="AL4" s="136" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="AM4" s="136"/>
       <c r="AN4" s="136"/>
@@ -19894,7 +19939,7 @@
       <c r="AS4" s="136"/>
       <c r="AT4" s="136"/>
       <c r="AU4" s="136" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="AV4" s="136"/>
       <c r="AW4" s="136"/>
@@ -19905,7 +19950,7 @@
       <c r="BB4" s="136"/>
       <c r="BC4" s="136"/>
       <c r="BD4" s="136" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="BE4" s="136"/>
       <c r="BF4" s="136"/>
@@ -19916,7 +19961,7 @@
       <c r="BK4" s="136"/>
       <c r="BL4" s="136"/>
       <c r="BM4" s="136" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="BN4" s="136"/>
       <c r="BO4" s="136"/>
@@ -19927,7 +19972,7 @@
       <c r="BT4" s="136"/>
       <c r="BU4" s="136"/>
       <c r="BV4" s="136" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="BW4" s="136"/>
       <c r="BX4" s="136"/>
@@ -19938,7 +19983,7 @@
       <c r="CC4" s="136"/>
       <c r="CD4" s="136"/>
       <c r="CE4" s="136" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="CF4" s="136"/>
       <c r="CG4" s="136"/>
@@ -19949,7 +19994,7 @@
       <c r="CL4" s="136"/>
       <c r="CM4" s="136"/>
       <c r="CN4" s="136" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="CO4" s="136"/>
       <c r="CP4" s="136"/>
@@ -19960,7 +20005,7 @@
       <c r="CU4" s="136"/>
       <c r="CV4" s="136"/>
       <c r="CW4" s="136" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="CX4" s="136"/>
       <c r="CY4" s="136"/>
@@ -19973,7 +20018,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="137" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B5" s="138" t="n">
         <v>1</v>
@@ -20300,19 +20345,19 @@
         <v>108</v>
       </c>
       <c r="DF5" s="140" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="DG5" s="140"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="137" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="DF6" s="139" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="DG6" s="139" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20757,7 +20802,7 @@
         <v>50</v>
       </c>
       <c r="DG7" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21202,7 +21247,7 @@
         <v>50</v>
       </c>
       <c r="DG8" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21647,7 +21692,7 @@
         <v>50</v>
       </c>
       <c r="DG9" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22092,7 +22137,7 @@
         <v>48</v>
       </c>
       <c r="DG10" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22537,7 +22582,7 @@
         <v>48</v>
       </c>
       <c r="DG11" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22982,7 +23027,7 @@
         <v>36</v>
       </c>
       <c r="DG12" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23427,7 +23472,7 @@
         <v>33</v>
       </c>
       <c r="DG13" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23872,7 +23917,7 @@
         <v>33</v>
       </c>
       <c r="DG14" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24317,7 +24362,7 @@
         <v>33</v>
       </c>
       <c r="DG15" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24762,7 +24807,7 @@
         <v>33</v>
       </c>
       <c r="DG16" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25207,7 +25252,7 @@
         <v>33</v>
       </c>
       <c r="DG17" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25652,7 +25697,7 @@
         <v>33</v>
       </c>
       <c r="DG18" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26097,7 +26142,7 @@
         <v>33</v>
       </c>
       <c r="DG19" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26542,7 +26587,7 @@
         <v>3</v>
       </c>
       <c r="DG20" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26987,7 +27032,7 @@
         <v>20</v>
       </c>
       <c r="DG21" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27432,7 +27477,7 @@
         <v>0</v>
       </c>
       <c r="DG22" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27877,7 +27922,7 @@
         <v>0</v>
       </c>
       <c r="DG23" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28322,45 +28367,45 @@
         <v>3</v>
       </c>
       <c r="DG24" s="139" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="128" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B27" s="145" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="C27" s="146" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="D27" s="146"/>
       <c r="E27" s="146"/>
       <c r="F27" s="146"/>
       <c r="G27" s="147" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="H27" s="146" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="I27" s="146"/>
       <c r="J27" s="146"/>
       <c r="K27" s="146"/>
       <c r="L27" s="148" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="M27" s="146" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="N27" s="146"/>
       <c r="O27" s="146"/>
       <c r="P27" s="146"/>
       <c r="Q27" s="149" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="R27" s="146" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="S27" s="146"/>
       <c r="T27" s="146"/>
@@ -28368,7 +28413,7 @@
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
